--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -968,7 +968,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$78</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2820" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3179" uniqueCount="593">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1269,6 +1269,98 @@
   </si>
   <si>
     <t>Outpat.VExam.AbnormalNormal</t>
+  </si>
+  <si>
+    <t>Observation.interpretation.id</t>
+  </si>
+  <si>
+    <t>Observation.interpretation.extension</t>
+  </si>
+  <si>
+    <t>Observation.interpretation.extension:11179-permitted-value-conceptmap</t>
+  </si>
+  <si>
+    <t>11179-permitted-value-conceptmap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {11179-permitted-value-conceptmap}
+</t>
+  </si>
+  <si>
+    <t>Mapping from permitted to transmitted</t>
+  </si>
+  <si>
+    <t>Expresses the linkage between the internal codes used for storage and the codes used for exchange.</t>
+  </si>
+  <si>
+    <t>The permitted value set must have a 1..1 set of codes for each code in the value meaning value set.  The source for the concept map is the value set the extension appears on.  The target is the permitted-value-valueset.</t>
+  </si>
+  <si>
+    <t>Observation.interpretation.extension:11179-permitted-value-conceptmap.id</t>
+  </si>
+  <si>
+    <t>Observation.interpretation.extension.id</t>
+  </si>
+  <si>
+    <t>Observation.interpretation.extension:11179-permitted-value-conceptmap.extension</t>
+  </si>
+  <si>
+    <t>Observation.interpretation.extension.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>Observation.interpretation.extension:11179-permitted-value-conceptmap.url</t>
+  </si>
+  <si>
+    <t>Observation.interpretation.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/11179-permitted-value-conceptmap</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Observation.interpretation.extension:11179-permitted-value-conceptmap.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.interpretation.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(ConceptMap)
+</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ConceptMap/CMVFExamResultInterpretation</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.interpretation.coding</t>
+  </si>
+  <si>
+    <t>Observation.interpretation.text</t>
   </si>
   <si>
     <t>Observation.note</t>
@@ -2088,12 +2180,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR69"/>
+  <dimension ref="A1:AR78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="45.1171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="78.4609375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="17.96484375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="34.3203125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -6976,7 +7068,7 @@
         <v>82</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>84</v>
@@ -6988,20 +7080,16 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>404</v>
+        <v>220</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>405</v>
+        <v>221</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>408</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>84</v>
       </c>
@@ -7049,19 +7137,19 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>403</v>
+        <v>223</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>84</v>
@@ -7070,10 +7158,10 @@
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>409</v>
+        <v>84</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>410</v>
+        <v>224</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>84</v>
@@ -7090,21 +7178,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>84</v>
@@ -7116,15 +7204,17 @@
         <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>220</v>
+        <v>141</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>221</v>
+        <v>142</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7161,31 +7251,31 @@
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>84</v>
+        <v>227</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>84</v>
+        <v>228</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>84</v>
+        <v>229</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>84</v>
@@ -7214,21 +7304,23 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="C41" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="D41" t="s" s="2">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>84</v>
@@ -7240,16 +7332,16 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>141</v>
+        <v>407</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>142</v>
+        <v>408</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>226</v>
+        <v>409</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>144</v>
+        <v>410</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7287,16 +7379,16 @@
         <v>84</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>227</v>
+        <v>84</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>228</v>
+        <v>84</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>229</v>
+        <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>230</v>
@@ -7320,10 +7412,10 @@
         <v>84</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>224</v>
+        <v>138</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>84</v>
@@ -7340,10 +7432,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7363,20 +7455,18 @@
         <v>84</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>414</v>
+        <v>220</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>415</v>
+        <v>221</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>84</v>
@@ -7425,7 +7515,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>418</v>
+        <v>223</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7437,7 +7527,7 @@
         <v>84</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>84</v>
@@ -7446,10 +7536,10 @@
         <v>84</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>419</v>
+        <v>224</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>84</v>
@@ -7466,10 +7556,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7480,7 +7570,7 @@
         <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>84</v>
@@ -7489,16 +7579,16 @@
         <v>84</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>293</v>
+        <v>141</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7537,31 +7627,31 @@
         <v>84</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>84</v>
+        <v>227</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>84</v>
+        <v>228</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>84</v>
+        <v>229</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>423</v>
+        <v>230</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>84</v>
@@ -7570,10 +7660,10 @@
         <v>84</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>424</v>
+        <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>84</v>
@@ -7590,10 +7680,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7607,31 +7697,33 @@
         <v>95</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>426</v>
+        <v>109</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>420</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>84</v>
+        <v>422</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>84</v>
@@ -7673,7 +7765,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>95</v>
@@ -7685,7 +7777,7 @@
         <v>84</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>84</v>
@@ -7694,11 +7786,11 @@
         <v>84</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="AN44" t="s" s="2">
-        <v>430</v>
-      </c>
       <c r="AO44" t="s" s="2">
         <v>84</v>
       </c>
@@ -7706,18 +7798,18 @@
         <v>84</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>431</v>
+        <v>84</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>432</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7725,7 +7817,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>95</v>
@@ -7740,17 +7832,15 @@
         <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>194</v>
+        <v>426</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -7760,7 +7850,7 @@
         <v>84</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>84</v>
+        <v>429</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>84</v>
@@ -7775,13 +7865,13 @@
         <v>84</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>210</v>
+        <v>84</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>437</v>
+        <v>84</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>438</v>
+        <v>84</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
@@ -7799,7 +7889,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7817,19 +7907,19 @@
         <v>84</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>439</v>
+        <v>84</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>440</v>
+        <v>84</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>441</v>
+        <v>138</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>442</v>
+        <v>84</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7840,10 +7930,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7854,7 +7944,7 @@
         <v>82</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>84</v>
@@ -7863,22 +7953,22 @@
         <v>84</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>194</v>
+        <v>232</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>444</v>
+        <v>233</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>445</v>
+        <v>234</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>446</v>
+        <v>235</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>447</v>
+        <v>236</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -7903,13 +7993,13 @@
         <v>84</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>210</v>
+        <v>84</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>448</v>
+        <v>84</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>449</v>
+        <v>84</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -7927,13 +8017,13 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>443</v>
+        <v>237</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>84</v>
@@ -7948,10 +8038,10 @@
         <v>84</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>450</v>
+        <v>238</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>451</v>
+        <v>239</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>84</v>
@@ -7968,10 +8058,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7991,21 +8081,23 @@
         <v>84</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>453</v>
+        <v>220</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>454</v>
+        <v>242</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>455</v>
+        <v>243</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
       </c>
@@ -8053,7 +8145,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>452</v>
+        <v>246</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8071,19 +8163,19 @@
         <v>84</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>457</v>
+        <v>84</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>458</v>
+        <v>247</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>459</v>
+        <v>248</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>460</v>
+        <v>84</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8094,10 +8186,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>461</v>
+        <v>433</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>461</v>
+        <v>433</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8108,7 +8200,7 @@
         <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>84</v>
@@ -8120,18 +8212,20 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>462</v>
+        <v>434</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>463</v>
+        <v>435</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>464</v>
+        <v>436</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>437</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>438</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
       </c>
@@ -8179,13 +8273,13 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>461</v>
+        <v>433</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>84</v>
@@ -8197,19 +8291,19 @@
         <v>84</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>466</v>
+        <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>467</v>
+        <v>439</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>468</v>
+        <v>440</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>469</v>
+        <v>84</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8220,10 +8314,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>470</v>
+        <v>441</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>470</v>
+        <v>441</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8234,7 +8328,7 @@
         <v>82</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>84</v>
@@ -8246,20 +8340,16 @@
         <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>471</v>
+        <v>220</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>472</v>
+        <v>221</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>475</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>84</v>
       </c>
@@ -8307,19 +8397,19 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>470</v>
+        <v>223</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>476</v>
+        <v>84</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>84</v>
@@ -8328,10 +8418,10 @@
         <v>84</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>477</v>
+        <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>478</v>
+        <v>224</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>84</v>
@@ -8348,21 +8438,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>479</v>
+        <v>442</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>479</v>
+        <v>442</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>84</v>
@@ -8374,15 +8464,17 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>220</v>
+        <v>141</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>221</v>
+        <v>142</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8419,31 +8511,31 @@
         <v>84</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>84</v>
+        <v>227</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>84</v>
+        <v>228</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>84</v>
+        <v>229</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>84</v>
@@ -8472,21 +8564,21 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>480</v>
+        <v>443</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>480</v>
+        <v>443</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>84</v>
@@ -8495,19 +8587,19 @@
         <v>84</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>141</v>
+        <v>444</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>142</v>
+        <v>445</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>226</v>
+        <v>446</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>144</v>
+        <v>447</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8557,19 +8649,19 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>230</v>
+        <v>448</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>84</v>
@@ -8578,10 +8670,10 @@
         <v>84</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>224</v>
+        <v>449</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>84</v>
@@ -8598,46 +8690,42 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>481</v>
+        <v>450</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>481</v>
+        <v>450</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>482</v>
+        <v>84</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="J52" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>141</v>
+        <v>293</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>483</v>
+        <v>451</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>84</v>
       </c>
@@ -8685,19 +8773,19 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>485</v>
+        <v>453</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>84</v>
@@ -8706,10 +8794,10 @@
         <v>84</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>138</v>
+        <v>454</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>84</v>
@@ -8726,10 +8814,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>486</v>
+        <v>455</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>486</v>
+        <v>455</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8737,28 +8825,28 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>487</v>
+        <v>456</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>488</v>
+        <v>457</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>489</v>
+        <v>458</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8809,16 +8897,16 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>486</v>
+        <v>459</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>490</v>
+        <v>84</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>107</v>
@@ -8830,10 +8918,10 @@
         <v>84</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>491</v>
+        <v>138</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>492</v>
+        <v>460</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>84</v>
@@ -8842,18 +8930,18 @@
         <v>84</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>84</v>
+        <v>461</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>84</v>
+        <v>462</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>493</v>
+        <v>463</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>493</v>
+        <v>463</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8876,15 +8964,17 @@
         <v>84</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>487</v>
+        <v>194</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>494</v>
+        <v>464</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -8909,13 +8999,13 @@
         <v>84</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>84</v>
+        <v>210</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>84</v>
+        <v>467</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>84</v>
+        <v>468</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>84</v>
@@ -8933,7 +9023,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>493</v>
+        <v>463</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -8942,7 +9032,7 @@
         <v>95</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>490</v>
+        <v>84</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>107</v>
@@ -8951,19 +9041,19 @@
         <v>84</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>84</v>
+        <v>469</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>491</v>
+        <v>470</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>496</v>
+        <v>471</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>84</v>
+        <v>472</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -8974,10 +9064,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>497</v>
+        <v>473</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>497</v>
+        <v>473</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9003,16 +9093,16 @@
         <v>194</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>498</v>
+        <v>474</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>499</v>
+        <v>475</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>500</v>
+        <v>476</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>501</v>
+        <v>477</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -9037,13 +9127,13 @@
         <v>84</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>119</v>
+        <v>210</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>502</v>
+        <v>478</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>503</v>
+        <v>479</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>84</v>
@@ -9061,7 +9151,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>497</v>
+        <v>473</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9079,13 +9169,13 @@
         <v>84</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>504</v>
+        <v>84</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>505</v>
+        <v>480</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>399</v>
+        <v>481</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>84</v>
@@ -9102,10 +9192,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>506</v>
+        <v>482</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>506</v>
+        <v>482</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9116,7 +9206,7 @@
         <v>82</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>84</v>
@@ -9128,20 +9218,18 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>194</v>
+        <v>483</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>507</v>
+        <v>484</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>508</v>
+        <v>485</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>510</v>
-      </c>
+        <v>486</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>84</v>
       </c>
@@ -9165,13 +9253,13 @@
         <v>84</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>210</v>
+        <v>84</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>511</v>
+        <v>84</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>512</v>
+        <v>84</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>84</v>
@@ -9189,13 +9277,13 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>506</v>
+        <v>482</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>84</v>
@@ -9207,19 +9295,19 @@
         <v>84</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>504</v>
+        <v>487</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>505</v>
+        <v>488</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>399</v>
+        <v>489</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>84</v>
+        <v>490</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9230,10 +9318,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>513</v>
+        <v>491</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>513</v>
+        <v>491</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9256,18 +9344,18 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>514</v>
+        <v>492</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>515</v>
+        <v>493</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" t="s" s="2">
-        <v>517</v>
-      </c>
+        <v>494</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>84</v>
       </c>
@@ -9315,7 +9403,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>513</v>
+        <v>491</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9333,19 +9421,19 @@
         <v>84</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>84</v>
+        <v>496</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>84</v>
+        <v>497</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>518</v>
+        <v>498</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>84</v>
+        <v>499</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9356,10 +9444,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>519</v>
+        <v>500</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>519</v>
+        <v>500</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9370,7 +9458,7 @@
         <v>82</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>84</v>
@@ -9382,16 +9470,20 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>220</v>
+        <v>501</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>520</v>
+        <v>502</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>503</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
       </c>
@@ -9439,19 +9531,19 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>519</v>
+        <v>500</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>107</v>
+        <v>506</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>84</v>
@@ -9460,10 +9552,10 @@
         <v>84</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>491</v>
+        <v>507</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>522</v>
+        <v>508</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>84</v>
@@ -9480,10 +9572,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>523</v>
+        <v>509</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>523</v>
+        <v>509</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9494,7 +9586,7 @@
         <v>82</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>84</v>
@@ -9503,20 +9595,18 @@
         <v>84</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>524</v>
+        <v>220</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>525</v>
+        <v>221</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>527</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9565,19 +9655,19 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>523</v>
+        <v>223</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>84</v>
@@ -9586,10 +9676,10 @@
         <v>84</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>528</v>
+        <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>529</v>
+        <v>224</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>84</v>
@@ -9606,14 +9696,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9629,19 +9719,19 @@
         <v>84</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>531</v>
+        <v>141</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>532</v>
+        <v>142</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>533</v>
+        <v>226</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>534</v>
+        <v>144</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9691,7 +9781,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>530</v>
+        <v>230</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9703,7 +9793,7 @@
         <v>84</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>84</v>
@@ -9712,10 +9802,10 @@
         <v>84</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>528</v>
+        <v>84</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>535</v>
+        <v>224</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>84</v>
@@ -9732,14 +9822,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>536</v>
+        <v>511</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>536</v>
+        <v>511</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>84</v>
+        <v>512</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9752,25 +9842,25 @@
         <v>84</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="J61" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>471</v>
+        <v>141</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>537</v>
+        <v>513</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>538</v>
+        <v>514</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>539</v>
+        <v>144</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>540</v>
+        <v>150</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -9819,7 +9909,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>536</v>
+        <v>515</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9831,7 +9921,7 @@
         <v>84</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>84</v>
@@ -9840,10 +9930,10 @@
         <v>84</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>541</v>
+        <v>84</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>542</v>
+        <v>138</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>84</v>
@@ -9860,10 +9950,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>543</v>
+        <v>516</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>543</v>
+        <v>516</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9886,13 +9976,13 @@
         <v>84</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>220</v>
+        <v>517</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>221</v>
+        <v>518</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>222</v>
+        <v>519</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9943,7 +10033,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>223</v>
+        <v>516</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -9952,10 +10042,10 @@
         <v>95</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>84</v>
+        <v>520</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>84</v>
@@ -9964,10 +10054,10 @@
         <v>84</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>84</v>
+        <v>521</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>224</v>
+        <v>522</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>84</v>
@@ -9984,21 +10074,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>544</v>
+        <v>523</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>544</v>
+        <v>523</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>84</v>
@@ -10010,17 +10100,15 @@
         <v>84</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>141</v>
+        <v>517</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>142</v>
+        <v>524</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>525</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -10069,19 +10157,19 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>230</v>
+        <v>523</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>84</v>
+        <v>520</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>84</v>
@@ -10090,10 +10178,10 @@
         <v>84</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>84</v>
+        <v>521</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>224</v>
+        <v>526</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>84</v>
@@ -10110,45 +10198,45 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>545</v>
+        <v>527</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>545</v>
+        <v>527</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>482</v>
+        <v>84</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>141</v>
+        <v>194</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>483</v>
+        <v>528</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>484</v>
+        <v>529</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>144</v>
+        <v>530</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>150</v>
+        <v>531</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10173,13 +10261,13 @@
         <v>84</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>84</v>
+        <v>532</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>84</v>
+        <v>533</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>84</v>
@@ -10197,31 +10285,31 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>485</v>
+        <v>527</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>84</v>
+        <v>534</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>84</v>
+        <v>535</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>138</v>
+        <v>399</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>84</v>
@@ -10238,10 +10326,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10249,10 +10337,10 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>84</v>
@@ -10261,22 +10349,22 @@
         <v>84</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K65" t="s" s="2">
         <v>194</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>209</v>
+        <v>540</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -10304,10 +10392,10 @@
         <v>210</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>211</v>
+        <v>541</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>212</v>
+        <v>542</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>84</v>
@@ -10325,13 +10413,13 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>84</v>
@@ -10343,16 +10431,16 @@
         <v>84</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>550</v>
+        <v>534</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>215</v>
+        <v>535</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>216</v>
+        <v>399</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>217</v>
+        <v>84</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>84</v>
@@ -10366,10 +10454,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10389,22 +10477,20 @@
         <v>84</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>315</v>
+        <v>544</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>553</v>
-      </c>
+        <v>546</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>319</v>
+        <v>547</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
@@ -10453,7 +10539,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10471,19 +10557,19 @@
         <v>84</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>554</v>
+        <v>84</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>322</v>
+        <v>84</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>323</v>
+        <v>548</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>324</v>
+        <v>84</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -10494,10 +10580,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10520,20 +10606,16 @@
         <v>84</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>551</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>84</v>
       </c>
@@ -10557,13 +10639,13 @@
         <v>84</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>384</v>
+        <v>84</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>385</v>
+        <v>84</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>386</v>
+        <v>84</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>84</v>
@@ -10581,7 +10663,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10590,7 +10672,7 @@
         <v>95</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>387</v>
+        <v>84</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>107</v>
@@ -10602,10 +10684,10 @@
         <v>84</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>138</v>
+        <v>521</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>388</v>
+        <v>552</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>84</v>
@@ -10622,14 +10704,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>390</v>
+        <v>84</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10645,23 +10727,21 @@
         <v>84</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>194</v>
+        <v>554</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>391</v>
+        <v>555</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>392</v>
+        <v>556</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>394</v>
-      </c>
+        <v>557</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>84</v>
       </c>
@@ -10685,13 +10765,13 @@
         <v>84</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>384</v>
+        <v>84</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>395</v>
+        <v>84</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>396</v>
+        <v>84</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>84</v>
@@ -10709,7 +10789,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -10727,19 +10807,19 @@
         <v>84</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>397</v>
+        <v>84</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>398</v>
+        <v>558</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>399</v>
+        <v>559</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>400</v>
+        <v>84</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
@@ -10773,23 +10853,21 @@
         <v>84</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>85</v>
+        <v>561</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>475</v>
-      </c>
+        <v>564</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>84</v>
       </c>
@@ -10858,10 +10936,10 @@
         <v>84</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>477</v>
+        <v>558</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>478</v>
+        <v>565</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>84</v>
@@ -10873,11 +10951,1157 @@
         <v>84</v>
       </c>
       <c r="AR69" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR70" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR71" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR72" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR73" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR74" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AQ75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR75" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR76" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="P77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP77" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AQ77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR77" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="P78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR78" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR69">
+  <autoFilter ref="A1:AR78">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10887,7 +12111,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI68">
+  <conditionalFormatting sqref="A2:AI77">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3179" uniqueCount="593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3179" uniqueCount="595">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -591,6 +591,9 @@
     <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
   </si>
   <si>
+    <t>final</t>
+  </si>
+  <si>
     <t>required</t>
   </si>
   <si>
@@ -615,7 +618,7 @@
     <t>FiveWs.status</t>
   </si>
   <si>
-    <t>1589: fixed value = final</t>
+    <t>1589: fixed value = #final</t>
   </si>
   <si>
     <t>Observation.category</t>
@@ -637,6 +640,14 @@
     <t>Used for filtering what observations are retrieved and displayed.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/observation-category"/&gt;
+    &lt;code value="exam"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
@@ -649,7 +660,7 @@
     <t>FiveWs.class</t>
   </si>
   <si>
-    <t>1591: fixed value = http://terminology.hl7.org/CodeSystem/observation-category|exam</t>
+    <t>1591: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#exam</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -3924,7 +3935,7 @@
         <v>84</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>84</v>
+        <v>184</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>84</v>
@@ -3939,13 +3950,13 @@
         <v>84</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>84</v>
@@ -3978,25 +3989,25 @@
         <v>107</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AR14" t="s" s="2">
         <v>84</v>
@@ -4004,10 +4015,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4030,19 +4041,19 @@
         <v>84</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>84</v>
@@ -4052,7 +4063,7 @@
         <v>84</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>84</v>
+        <v>200</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>84</v>
@@ -4070,10 +4081,10 @@
         <v>119</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>84</v>
@@ -4091,7 +4102,7 @@
         <v>84</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>82</v>
@@ -4115,16 +4126,16 @@
         <v>84</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ15" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AR15" t="s" s="2">
         <v>84</v>
@@ -4132,14 +4143,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4158,19 +4169,19 @@
         <v>96</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>84</v>
@@ -4195,13 +4206,13 @@
         <v>84</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>84</v>
@@ -4219,7 +4230,7 @@
         <v>84</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>95</v>
@@ -4234,22 +4245,22 @@
         <v>107</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>84</v>
@@ -4260,10 +4271,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4286,13 +4297,13 @@
         <v>84</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4343,7 +4354,7 @@
         <v>84</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>82</v>
@@ -4367,7 +4378,7 @@
         <v>84</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>84</v>
@@ -4384,10 +4395,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4416,7 +4427,7 @@
         <v>142</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>144</v>
@@ -4457,19 +4468,19 @@
         <v>84</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4493,7 +4504,7 @@
         <v>84</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>84</v>
@@ -4510,10 +4521,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4536,19 +4547,19 @@
         <v>96</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>84</v>
@@ -4597,7 +4608,7 @@
         <v>84</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -4618,10 +4629,10 @@
         <v>84</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>84</v>
@@ -4630,7 +4641,7 @@
         <v>84</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AR19" t="s" s="2">
         <v>84</v>
@@ -4638,10 +4649,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4664,19 +4675,19 @@
         <v>96</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>84</v>
@@ -4725,7 +4736,7 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -4746,10 +4757,10 @@
         <v>84</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>84</v>
@@ -4766,10 +4777,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4792,19 +4803,19 @@
         <v>96</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>84</v>
@@ -4853,7 +4864,7 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -4868,25 +4879,25 @@
         <v>107</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AR21" t="s" s="2">
         <v>84</v>
@@ -4894,10 +4905,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4920,16 +4931,16 @@
         <v>96</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4979,7 +4990,7 @@
         <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -5000,13 +5011,13 @@
         <v>84</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>84</v>
@@ -5020,14 +5031,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5046,19 +5057,19 @@
         <v>96</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>84</v>
@@ -5107,7 +5118,7 @@
         <v>84</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -5122,40 +5133,40 @@
         <v>107</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5174,19 +5185,19 @@
         <v>96</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
@@ -5223,17 +5234,17 @@
         <v>84</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AC24" s="2"/>
       <c r="AD24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5248,19 +5259,19 @@
         <v>107</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>84</v>
@@ -5274,16 +5285,16 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5302,19 +5313,19 @@
         <v>96</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5363,7 +5374,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5378,36 +5389,36 @@
         <v>107</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5430,16 +5441,16 @@
         <v>96</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5489,7 +5500,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5510,13 +5521,13 @@
         <v>84</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>84</v>
@@ -5530,10 +5541,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5556,17 +5567,17 @@
         <v>96</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>84</v>
@@ -5615,7 +5626,7 @@
         <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5630,25 +5641,25 @@
         <v>107</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>84</v>
@@ -5656,10 +5667,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5682,19 +5693,19 @@
         <v>96</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5731,17 +5742,17 @@
         <v>84</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5750,7 +5761,7 @@
         <v>95</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>107</v>
@@ -5759,19 +5770,19 @@
         <v>84</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
@@ -5782,13 +5793,13 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>84</v>
@@ -5810,19 +5821,19 @@
         <v>96</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5871,7 +5882,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5880,7 +5891,7 @@
         <v>95</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>107</v>
@@ -5889,22 +5900,22 @@
         <v>84</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AR29" t="s" s="2">
         <v>84</v>
@@ -5912,10 +5923,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5938,13 +5949,13 @@
         <v>84</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5995,7 +6006,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6019,7 +6030,7 @@
         <v>84</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>84</v>
@@ -6036,10 +6047,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6068,7 +6079,7 @@
         <v>142</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>144</v>
@@ -6109,19 +6120,19 @@
         <v>84</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6145,7 +6156,7 @@
         <v>84</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>84</v>
@@ -6162,10 +6173,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6188,19 +6199,19 @@
         <v>96</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6249,7 +6260,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6270,10 +6281,10 @@
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>84</v>
@@ -6282,7 +6293,7 @@
         <v>84</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>84</v>
@@ -6290,10 +6301,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6319,20 +6330,20 @@
         <v>115</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q33" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="R33" t="s" s="2">
         <v>84</v>
@@ -6353,13 +6364,13 @@
         <v>84</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>84</v>
@@ -6377,7 +6388,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6398,10 +6409,10 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>84</v>
@@ -6418,10 +6429,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6444,17 +6455,17 @@
         <v>96</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6503,7 +6514,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6524,10 +6535,10 @@
         <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>84</v>
@@ -6544,10 +6555,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6573,14 +6584,14 @@
         <v>109</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6629,7 +6640,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6638,7 +6649,7 @@
         <v>95</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>107</v>
@@ -6650,10 +6661,10 @@
         <v>84</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>84</v>
@@ -6670,10 +6681,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6699,16 +6710,16 @@
         <v>115</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6757,7 +6768,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6778,10 +6789,10 @@
         <v>84</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>84</v>
@@ -6798,10 +6809,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6824,19 +6835,19 @@
         <v>84</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6861,13 +6872,13 @@
         <v>84</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>84</v>
@@ -6885,7 +6896,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6894,7 +6905,7 @@
         <v>95</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>107</v>
@@ -6909,7 +6920,7 @@
         <v>138</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>84</v>
@@ -6926,14 +6937,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6952,19 +6963,19 @@
         <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -6989,13 +7000,13 @@
         <v>84</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>84</v>
@@ -7013,7 +7024,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7031,33 +7042,33 @@
         <v>84</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7080,13 +7091,13 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7137,7 +7148,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7161,7 +7172,7 @@
         <v>84</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>84</v>
@@ -7178,10 +7189,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7210,7 +7221,7 @@
         <v>142</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>144</v>
@@ -7251,19 +7262,19 @@
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7287,7 +7298,7 @@
         <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>84</v>
@@ -7304,13 +7315,13 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>84</v>
@@ -7332,16 +7343,16 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7391,7 +7402,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7432,10 +7443,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7458,13 +7469,13 @@
         <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7515,7 +7526,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7539,7 +7550,7 @@
         <v>84</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>84</v>
@@ -7556,10 +7567,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7585,10 +7596,10 @@
         <v>141</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7627,19 +7638,19 @@
         <v>84</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7680,10 +7691,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7709,13 +7720,13 @@
         <v>109</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7723,7 +7734,7 @@
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>84</v>
@@ -7765,7 +7776,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>95</v>
@@ -7806,10 +7817,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7832,13 +7843,13 @@
         <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7850,7 +7861,7 @@
         <v>84</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>84</v>
@@ -7889,7 +7900,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7930,10 +7941,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7956,19 +7967,19 @@
         <v>96</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -8017,7 +8028,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8038,10 +8049,10 @@
         <v>84</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>84</v>
@@ -8058,10 +8069,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8084,19 +8095,19 @@
         <v>96</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
@@ -8145,7 +8156,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8166,10 +8177,10 @@
         <v>84</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>84</v>
@@ -8186,10 +8197,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8212,19 +8223,19 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8273,7 +8284,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8294,10 +8305,10 @@
         <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>84</v>
@@ -8314,10 +8325,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8340,13 +8351,13 @@
         <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8397,7 +8408,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8421,7 +8432,7 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>84</v>
@@ -8438,10 +8449,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8470,7 +8481,7 @@
         <v>142</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>144</v>
@@ -8511,19 +8522,19 @@
         <v>84</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8547,7 +8558,7 @@
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>84</v>
@@ -8564,10 +8575,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8590,16 +8601,16 @@
         <v>96</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8649,7 +8660,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8673,7 +8684,7 @@
         <v>138</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>84</v>
@@ -8690,10 +8701,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8716,13 +8727,13 @@
         <v>96</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8773,7 +8784,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8797,7 +8808,7 @@
         <v>138</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>84</v>
@@ -8814,10 +8825,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8840,13 +8851,13 @@
         <v>96</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8897,7 +8908,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>95</v>
@@ -8921,7 +8932,7 @@
         <v>138</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>84</v>
@@ -8930,18 +8941,18 @@
         <v>84</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8964,16 +8975,16 @@
         <v>84</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8999,13 +9010,13 @@
         <v>84</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>84</v>
@@ -9023,7 +9034,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9041,19 +9052,19 @@
         <v>84</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -9064,10 +9075,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9090,19 +9101,19 @@
         <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -9127,13 +9138,13 @@
         <v>84</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>84</v>
@@ -9151,7 +9162,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9172,10 +9183,10 @@
         <v>84</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>84</v>
@@ -9192,10 +9203,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9218,16 +9229,16 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9277,7 +9288,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9295,19 +9306,19 @@
         <v>84</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9318,10 +9329,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9344,16 +9355,16 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9403,7 +9414,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9421,19 +9432,19 @@
         <v>84</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9444,10 +9455,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9470,19 +9481,19 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9531,7 +9542,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9543,7 +9554,7 @@
         <v>84</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>84</v>
@@ -9552,10 +9563,10 @@
         <v>84</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>84</v>
@@ -9572,10 +9583,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9598,13 +9609,13 @@
         <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9655,7 +9666,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9679,7 +9690,7 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>84</v>
@@ -9696,10 +9707,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9728,7 +9739,7 @@
         <v>142</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>144</v>
@@ -9781,7 +9792,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9805,7 +9816,7 @@
         <v>84</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>84</v>
@@ -9822,14 +9833,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9851,10 +9862,10 @@
         <v>141</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>144</v>
@@ -9909,7 +9920,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9950,10 +9961,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9976,13 +9987,13 @@
         <v>84</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10033,7 +10044,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10042,7 +10053,7 @@
         <v>95</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>107</v>
@@ -10054,10 +10065,10 @@
         <v>84</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>84</v>
@@ -10074,10 +10085,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10100,13 +10111,13 @@
         <v>84</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -10157,7 +10168,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10166,7 +10177,7 @@
         <v>95</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>107</v>
@@ -10178,10 +10189,10 @@
         <v>84</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>84</v>
@@ -10198,10 +10209,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10224,19 +10235,19 @@
         <v>84</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10264,10 +10275,10 @@
         <v>119</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>84</v>
@@ -10285,7 +10296,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10303,13 +10314,13 @@
         <v>84</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>84</v>
@@ -10326,10 +10337,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10352,19 +10363,19 @@
         <v>84</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -10389,13 +10400,13 @@
         <v>84</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>84</v>
@@ -10413,7 +10424,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10431,13 +10442,13 @@
         <v>84</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>84</v>
@@ -10454,10 +10465,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10480,17 +10491,17 @@
         <v>84</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
@@ -10539,7 +10550,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10563,7 +10574,7 @@
         <v>84</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>84</v>
@@ -10580,10 +10591,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10606,13 +10617,13 @@
         <v>84</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10663,7 +10674,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10684,10 +10695,10 @@
         <v>84</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>84</v>
@@ -10704,10 +10715,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10730,16 +10741,16 @@
         <v>96</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10789,7 +10800,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -10810,10 +10821,10 @@
         <v>84</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>84</v>
@@ -10830,10 +10841,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10856,16 +10867,16 @@
         <v>96</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10915,7 +10926,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -10936,10 +10947,10 @@
         <v>84</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>84</v>
@@ -10956,10 +10967,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10982,19 +10993,19 @@
         <v>96</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -11043,7 +11054,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11064,10 +11075,10 @@
         <v>84</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>84</v>
@@ -11084,10 +11095,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11110,13 +11121,13 @@
         <v>84</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -11167,7 +11178,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11191,7 +11202,7 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>84</v>
@@ -11208,10 +11219,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11240,7 +11251,7 @@
         <v>142</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>144</v>
@@ -11293,7 +11304,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11317,7 +11328,7 @@
         <v>84</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>84</v>
@@ -11334,14 +11345,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -11363,10 +11374,10 @@
         <v>141</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>144</v>
@@ -11421,7 +11432,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11462,10 +11473,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11488,19 +11499,19 @@
         <v>96</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>84</v>
@@ -11525,13 +11536,13 @@
         <v>84</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>84</v>
@@ -11549,7 +11560,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>95</v>
@@ -11567,16 +11578,16 @@
         <v>84</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>84</v>
@@ -11590,10 +11601,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11616,19 +11627,19 @@
         <v>96</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>84</v>
@@ -11677,7 +11688,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -11695,19 +11706,19 @@
         <v>84</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
@@ -11718,10 +11729,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11744,19 +11755,19 @@
         <v>84</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>84</v>
@@ -11781,13 +11792,13 @@
         <v>84</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>84</v>
@@ -11805,7 +11816,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -11814,7 +11825,7 @@
         <v>95</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>107</v>
@@ -11829,7 +11840,7 @@
         <v>138</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>84</v>
@@ -11846,14 +11857,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11872,19 +11883,19 @@
         <v>84</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -11909,13 +11920,13 @@
         <v>84</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>84</v>
@@ -11933,7 +11944,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -11951,19 +11962,19 @@
         <v>84</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
@@ -11974,10 +11985,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12003,16 +12014,16 @@
         <v>85</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>84</v>
@@ -12061,7 +12072,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12082,10 +12093,10 @@
         <v>84</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -775,7 +775,7 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
-    <t>1581: source value from V EXAM - EXAM &gt; EXAM - CODE MAPPINGS (#9000010.13-.01 &gt; 9999999.15-210)</t>
+    <t>1581: source value from V EXAM - EXAM &gt; EXAM - CODE MAPPINGS &gt; CODE MAPPINGS (#9000010.13-.01 &gt; 9999999.15-210&gt;9999999.18)</t>
   </si>
   <si>
     <t>Observation.code.text</t>
@@ -2235,7 +2235,7 @@
     <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="99.61328125" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="130.3515625" customWidth="true" bestFit="true"/>
     <col min="44" max="44" width="43.94140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -253,12 +259,6 @@
   </si>
   <si>
     <t>Mapping: SNOMED CT Attribute Binding</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t>Vital Signs
@@ -603,6 +603,9 @@
     <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
   </si>
   <si>
+    <t>1589: fixed value = #final</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -616,9 +619,6 @@
   </si>
   <si>
     <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>1589: fixed value = #final</t>
   </si>
   <si>
     <t>Observation.category</t>
@@ -654,13 +654,13 @@
     <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
+    <t>1591: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#exam</t>
+  </si>
+  <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
   </si>
   <si>
     <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>1591: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#exam</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -769,13 +769,13 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
+    <t>1581: source value from V EXAM - EXAM &gt; EXAM - CODE MAPPINGS &gt; CODE MAPPINGS (#9000010.13-.01 &gt; 9999999.15-210&gt;9999999.18)</t>
+  </si>
+  <si>
     <t>C*E.1-8, C*E.10-22</t>
   </si>
   <si>
     <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>1581: source value from V EXAM - EXAM &gt; EXAM - CODE MAPPINGS &gt; CODE MAPPINGS (#9000010.13-.01 &gt; 9999999.15-210&gt;9999999.18)</t>
   </si>
   <si>
     <t>Observation.code.text</t>
@@ -821,6 +821,9 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
+    <t>1582: reference from V EXAM - PATIENT NAME &gt; PATIENT/IHS - NAME (#9000010.13-.02 &gt; 9000001-.01)</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -831,9 +834,6 @@
   </si>
   <si>
     <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>1582: reference from V EXAM - PATIENT NAME &gt; PATIENT/IHS - NAME (#9000010.13-.02 &gt; 9000001-.01)</t>
   </si>
   <si>
     <t>Observation.focus</t>
@@ -878,6 +878,12 @@
     <t>For some observations it may be important to know the link between an observation and a particular encounter.</t>
   </si>
   <si>
+    <t>1583: reference from V EXAM - VISIT (#9000010.13-.03)</t>
+  </si>
+  <si>
+    <t>Outpat.VExam.VisitDateTime</t>
+  </si>
+  <si>
     <t>Event.context</t>
   </si>
   <si>
@@ -888,12 +894,6 @@
   </si>
   <si>
     <t>FiveWs.context</t>
-  </si>
-  <si>
-    <t>1583: reference from V EXAM - VISIT (#9000010.13-.03)</t>
-  </si>
-  <si>
-    <t>Outpat.VExam.VisitDateTime</t>
   </si>
   <si>
     <t>Observation.effective[x]</t>
@@ -992,6 +992,9 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
+    <t>1590: reference from V EXAM - ENCOUNTER PROVIDER (#9000010.13-1204)</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1002,9 +1005,6 @@
   </si>
   <si>
     <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>1590: reference from V EXAM - ENCOUNTER PROVIDER (#9000010.13-1204)</t>
   </si>
   <si>
     <t>Observation.value[x]</t>
@@ -1092,13 +1092,13 @@
     <t>Quantity.value</t>
   </si>
   <si>
+    <t>1585: source value from V EXAM - MAGNITUDE (#9000010.13-220)</t>
+  </si>
+  <si>
     <t>SN.2  / CQ - N/A</t>
   </si>
   <si>
     <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
-  </si>
-  <si>
-    <t>1585: source value from V EXAM - MAGNITUDE (#9000010.13-220)</t>
   </si>
   <si>
     <t>Observation.value[x]:valueQuantity.comparator</t>
@@ -1264,6 +1264,12 @@
     <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
   </si>
   <si>
+    <t>1584: transform using VF_ExamResultInterpretation on V EXAM - RESULT (#9000010.13-.04)</t>
+  </si>
+  <si>
+    <t>Outpat.VExam.AbnormalNormal</t>
+  </si>
+  <si>
     <t>&lt; 260245000 |Findings values|</t>
   </si>
   <si>
@@ -1274,12 +1280,6 @@
   </si>
   <si>
     <t>363713009 |Has interpretation|</t>
-  </si>
-  <si>
-    <t>1584: transform using VF_ExamResultInterpretation on V EXAM - RESULT (#9000010.13-.04)</t>
-  </si>
-  <si>
-    <t>Outpat.VExam.AbnormalNormal</t>
   </si>
   <si>
     <t>Observation.interpretation.id</t>
@@ -1458,13 +1458,13 @@
     <t>Annotation.text</t>
   </si>
   <si>
+    <t>1587: source value from V EXAM - COMMENTS (#9000010.13-81101)</t>
+  </si>
+  <si>
+    <t>Outpat.VExam.Comments</t>
+  </si>
+  <si>
     <t>Act.text</t>
-  </si>
-  <si>
-    <t>1587: source value from V EXAM - COMMENTS (#9000010.13-81101)</t>
-  </si>
-  <si>
-    <t>Outpat.VExam.Comments</t>
   </si>
   <si>
     <t>Observation.bodySite</t>
@@ -2229,14 +2229,14 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="130.3515625" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="130.3515625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="107.01953125" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="42.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2475,22 +2475,22 @@
         <v>89</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="AN2" t="s" s="2">
+      <c r="AP2" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP2" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ2" t="s" s="2">
         <v>84</v>
@@ -3112,13 +3112,13 @@
         <v>84</v>
       </c>
       <c r="AN7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP7" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP7" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ7" t="s" s="2">
         <v>84</v>
@@ -3238,13 +3238,13 @@
         <v>84</v>
       </c>
       <c r="AN8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP8" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP8" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ8" t="s" s="2">
         <v>84</v>
@@ -3364,13 +3364,13 @@
         <v>84</v>
       </c>
       <c r="AN9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP9" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="AO9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP9" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ9" t="s" s="2">
         <v>84</v>
@@ -3492,13 +3492,13 @@
         <v>84</v>
       </c>
       <c r="AN10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP10" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="AO10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP10" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ10" t="s" s="2">
         <v>84</v>
@@ -3609,25 +3609,25 @@
         <v>107</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AL11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO11" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="AO11" t="s" s="2">
+      <c r="AQ11" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ11" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR11" t="s" s="2">
         <v>84</v>
@@ -3735,22 +3735,22 @@
         <v>107</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="AL12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO12" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AN12" t="s" s="2">
+      <c r="AP12" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP12" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>84</v>
@@ -3861,22 +3861,22 @@
         <v>107</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AL13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO13" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="AN13" t="s" s="2">
+      <c r="AP13" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP13" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ13" t="s" s="2">
         <v>84</v>
@@ -3992,19 +3992,19 @@
         <v>188</v>
       </c>
       <c r="AL14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="AO14" t="s" s="2">
+      <c r="AP14" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AP14" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ14" t="s" s="2">
         <v>193</v>
@@ -4117,7 +4117,7 @@
         <v>107</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>84</v>
+        <v>203</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>84</v>
@@ -4126,13 +4126,13 @@
         <v>84</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>203</v>
+        <v>84</v>
       </c>
       <c r="AO15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP15" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>205</v>
@@ -4245,28 +4245,28 @@
         <v>107</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AP16" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AO16" t="s" s="2">
+      <c r="AQ16" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AP16" t="s" s="2">
+      <c r="AR16" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AQ16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR16" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="17" hidden="true">
@@ -4378,13 +4378,13 @@
         <v>84</v>
       </c>
       <c r="AN17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP17" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>84</v>
@@ -4504,13 +4504,13 @@
         <v>84</v>
       </c>
       <c r="AN18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP18" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>84</v>
@@ -4623,25 +4623,25 @@
         <v>107</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>84</v>
+        <v>240</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>240</v>
+        <v>84</v>
       </c>
       <c r="AN19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO19" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AO19" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AP19" t="s" s="2">
-        <v>84</v>
+        <v>242</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>242</v>
+        <v>84</v>
       </c>
       <c r="AR19" t="s" s="2">
         <v>84</v>
@@ -4757,16 +4757,16 @@
         <v>84</v>
       </c>
       <c r="AM20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>84</v>
@@ -4888,13 +4888,13 @@
         <v>258</v>
       </c>
       <c r="AN21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AO21" t="s" s="2">
+      <c r="AP21" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>261</v>
@@ -5011,19 +5011,19 @@
         <v>84</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="AO22" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AQ22" t="s" s="2">
-        <v>84</v>
+        <v>261</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>84</v>
@@ -5136,25 +5136,25 @@
         <v>275</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>84</v>
+        <v>276</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>277</v>
+        <v>84</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>278</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>84</v>
+        <v>279</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>280</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" hidden="true">
@@ -5259,25 +5259,25 @@
         <v>107</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AL24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="AO24" t="s" s="2">
+      <c r="AQ24" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>84</v>
@@ -5389,28 +5389,28 @@
         <v>107</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AL25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="AO25" t="s" s="2">
+      <c r="AQ25" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="AP25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ25" t="s" s="2">
-        <v>296</v>
-      </c>
       <c r="AR25" t="s" s="2">
-        <v>297</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" hidden="true">
@@ -5521,19 +5521,19 @@
         <v>84</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AP26" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AO26" t="s" s="2">
+      <c r="AQ26" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ26" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR26" t="s" s="2">
         <v>84</v>
@@ -5650,13 +5650,13 @@
         <v>312</v>
       </c>
       <c r="AN27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="AO27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>315</v>
@@ -5770,25 +5770,25 @@
         <v>84</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AP28" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="AO28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP28" t="s" s="2">
+      <c r="AQ28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR28" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AQ28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR28" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="29" hidden="true">
@@ -5897,28 +5897,28 @@
         <v>107</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>84</v>
+        <v>330</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="AN29" t="s" s="2">
+      <c r="AP29" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="AO29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP29" t="s" s="2">
+      <c r="AQ29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR29" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AQ29" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="AR29" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="30" hidden="true">
@@ -6030,13 +6030,13 @@
         <v>84</v>
       </c>
       <c r="AN30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP30" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>84</v>
@@ -6156,13 +6156,13 @@
         <v>84</v>
       </c>
       <c r="AN31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP31" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
@@ -6275,25 +6275,25 @@
         <v>107</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>84</v>
+        <v>343</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>343</v>
+        <v>84</v>
       </c>
       <c r="AN32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="AO32" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AP32" t="s" s="2">
-        <v>84</v>
+        <v>345</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>345</v>
+        <v>84</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>84</v>
@@ -6409,16 +6409,16 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AP33" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -6535,16 +6535,16 @@
         <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
@@ -6661,16 +6661,16 @@
         <v>84</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AP35" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -6789,16 +6789,16 @@
         <v>84</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AN36" t="s" s="2">
+      <c r="AP36" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -6917,16 +6917,16 @@
         <v>84</v>
       </c>
       <c r="AM37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO37" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AP37" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -7039,25 +7039,25 @@
         <v>107</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>84</v>
+        <v>399</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>400</v>
+        <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>401</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>84</v>
+        <v>402</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>403</v>
+        <v>84</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>404</v>
@@ -7172,13 +7172,13 @@
         <v>84</v>
       </c>
       <c r="AN39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP39" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -7298,13 +7298,13 @@
         <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP40" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -7423,16 +7423,16 @@
         <v>84</v>
       </c>
       <c r="AM41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AP41" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7550,13 +7550,13 @@
         <v>84</v>
       </c>
       <c r="AN42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP42" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7800,13 +7800,13 @@
         <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP44" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7924,13 +7924,13 @@
         <v>84</v>
       </c>
       <c r="AN45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP45" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -8049,16 +8049,16 @@
         <v>84</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>240</v>
+        <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO46" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AO46" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AP46" t="s" s="2">
-        <v>84</v>
+        <v>242</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -8177,16 +8177,16 @@
         <v>84</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AN47" t="s" s="2">
+      <c r="AP47" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8305,16 +8305,16 @@
         <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AP48" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8432,13 +8432,13 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8558,13 +8558,13 @@
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP50" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8681,16 +8681,16 @@
         <v>84</v>
       </c>
       <c r="AM51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO51" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AP51" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8805,16 +8805,16 @@
         <v>84</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AP52" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8923,28 +8923,28 @@
         <v>107</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>84</v>
+        <v>462</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>84</v>
+        <v>463</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="AN53" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AP53" t="s" s="2">
-        <v>84</v>
+        <v>464</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>463</v>
+        <v>84</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>464</v>
+        <v>84</v>
       </c>
     </row>
     <row r="54" hidden="true">
@@ -9052,25 +9052,25 @@
         <v>84</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AO54" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AN54" t="s" s="2">
+      <c r="AP54" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="AO54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP54" t="s" s="2">
+      <c r="AQ54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR54" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="AQ54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR54" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="55" hidden="true">
@@ -9183,16 +9183,16 @@
         <v>84</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AP55" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9306,25 +9306,25 @@
         <v>84</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="AM56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AP56" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="AO56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP56" t="s" s="2">
+      <c r="AQ56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR56" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="AQ56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR56" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="57" hidden="true">
@@ -9432,25 +9432,25 @@
         <v>84</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="AM57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="AN57" t="s" s="2">
+      <c r="AP57" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="AO57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP57" t="s" s="2">
+      <c r="AQ57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR57" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="AQ57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR57" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="58" hidden="true">
@@ -9563,16 +9563,16 @@
         <v>84</v>
       </c>
       <c r="AM58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO58" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AP58" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9690,13 +9690,13 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP59" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9816,13 +9816,13 @@
         <v>84</v>
       </c>
       <c r="AN60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP60" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9944,13 +9944,13 @@
         <v>84</v>
       </c>
       <c r="AN61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP61" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -10065,16 +10065,16 @@
         <v>84</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO62" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="AN62" t="s" s="2">
+      <c r="AP62" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10189,16 +10189,16 @@
         <v>84</v>
       </c>
       <c r="AM63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO63" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="AN63" t="s" s="2">
+      <c r="AP63" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10314,19 +10314,19 @@
         <v>84</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="AN64" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AP64" t="s" s="2">
-        <v>84</v>
+        <v>403</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10442,19 +10442,19 @@
         <v>84</v>
       </c>
       <c r="AL65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="AM65" t="s" s="2">
+      <c r="AO65" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="AN65" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AP65" t="s" s="2">
-        <v>84</v>
+        <v>403</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -10574,13 +10574,13 @@
         <v>84</v>
       </c>
       <c r="AN66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP66" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -10695,16 +10695,16 @@
         <v>84</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO67" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="AN67" t="s" s="2">
+      <c r="AP67" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
@@ -10821,16 +10821,16 @@
         <v>84</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO68" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="AN68" t="s" s="2">
+      <c r="AP68" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
@@ -10947,16 +10947,16 @@
         <v>84</v>
       </c>
       <c r="AM69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO69" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="AN69" t="s" s="2">
+      <c r="AP69" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -11075,16 +11075,16 @@
         <v>84</v>
       </c>
       <c r="AM70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO70" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="AN70" t="s" s="2">
+      <c r="AP70" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11202,13 +11202,13 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP71" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
@@ -11328,13 +11328,13 @@
         <v>84</v>
       </c>
       <c r="AN72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
@@ -11456,13 +11456,13 @@
         <v>84</v>
       </c>
       <c r="AN73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP73" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
@@ -11578,22 +11578,22 @@
         <v>84</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AO74" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AN74" t="s" s="2">
+      <c r="AP74" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AO74" t="s" s="2">
+      <c r="AQ74" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ74" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR74" t="s" s="2">
         <v>84</v>
@@ -11706,25 +11706,25 @@
         <v>84</v>
       </c>
       <c r="AL75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="AM75" t="s" s="2">
+      <c r="AO75" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="AN75" t="s" s="2">
+      <c r="AP75" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="AO75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP75" t="s" s="2">
+      <c r="AQ75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR75" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AQ75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR75" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="76" hidden="true">
@@ -11837,16 +11837,16 @@
         <v>84</v>
       </c>
       <c r="AM76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO76" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="AN76" t="s" s="2">
+      <c r="AP76" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
@@ -11962,25 +11962,25 @@
         <v>84</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>399</v>
+        <v>84</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>400</v>
+        <v>84</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>401</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>84</v>
+        <v>402</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>84</v>
+        <v>404</v>
       </c>
     </row>
     <row r="78" hidden="true">
@@ -12093,16 +12093,16 @@
         <v>84</v>
       </c>
       <c r="AM78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO78" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="AN78" t="s" s="2">
+      <c r="AP78" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP78" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file V EXAM (#9000010.13) to Observation</t>
+    <t>This StructureDefinition contains the maps for VistA file V EXAM (9000010.13) to Observation</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -769,7 +769,7 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>1581: source value from V EXAM - EXAM &gt; EXAM - CODE MAPPINGS &gt; CODE MAPPINGS (#9000010.13-.01 &gt; 9999999.15-210&gt;9999999.18)</t>
+    <t>1581: source value from V EXAM - EXAM &gt; EXAM - CODE MAPPINGS &gt; CODE MAPPINGS (9000010.13-.01 &gt; 9999999.15-210&gt;9999999.18)</t>
   </si>
   <si>
     <t>C*E.1-8, C*E.10-22</t>
@@ -821,7 +821,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>1582: reference from V EXAM - PATIENT NAME &gt; PATIENT/IHS - NAME (#9000010.13-.02 &gt; 9000001-.01)</t>
+    <t>1582: reference from V EXAM - PATIENT NAME &gt; PATIENT/IHS - NAME (9000010.13-.02 &gt; 9000001-.01)</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -878,7 +878,7 @@
     <t>For some observations it may be important to know the link between an observation and a particular encounter.</t>
   </si>
   <si>
-    <t>1583: reference from V EXAM - VISIT (#9000010.13-.03)</t>
+    <t>1583: reference from V EXAM - VISIT (9000010.13-.03)</t>
   </si>
   <si>
     <t>Outpat.VExam.VisitDateTime</t>
@@ -945,7 +945,7 @@
 </t>
   </si>
   <si>
-    <t>1588: source value from V EXAM - EVENT DATE AND TIME (#9000010.13-1201)</t>
+    <t>1588: source value from V EXAM - EVENT DATE AND TIME (9000010.13-1201)</t>
   </si>
   <si>
     <t>Outpat.VExam.EventDateTime</t>
@@ -992,7 +992,7 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
-    <t>1590: reference from V EXAM - ENCOUNTER PROVIDER (#9000010.13-1204)</t>
+    <t>1590: reference from V EXAM - ENCOUNTER PROVIDER (9000010.13-1204)</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1052,7 +1052,7 @@
 </t>
   </si>
   <si>
-    <t>1586: source value from V EXAM - UCUM CODE (#9000010.13-221)</t>
+    <t>1586: source value from V EXAM - UCUM CODE (9000010.13-221)</t>
   </si>
   <si>
     <t>Observation.value[x]:valueQuantity.id</t>
@@ -1092,7 +1092,7 @@
     <t>Quantity.value</t>
   </si>
   <si>
-    <t>1585: source value from V EXAM - MAGNITUDE (#9000010.13-220)</t>
+    <t>1585: source value from V EXAM - MAGNITUDE (9000010.13-220)</t>
   </si>
   <si>
     <t>SN.2  / CQ - N/A</t>
@@ -1264,7 +1264,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
   </si>
   <si>
-    <t>1584: transform using VF_ExamResultInterpretation on V EXAM - RESULT (#9000010.13-.04)</t>
+    <t>1584: transform using VF_ExamResultInterpretation on V EXAM - RESULT (9000010.13-.04)</t>
   </si>
   <si>
     <t>Outpat.VExam.AbnormalNormal</t>
@@ -1458,7 +1458,7 @@
     <t>Annotation.text</t>
   </si>
   <si>
-    <t>1587: source value from V EXAM - COMMENTS (#9000010.13-81101)</t>
+    <t>1587: source value from V EXAM - COMMENTS (9000010.13-81101)</t>
   </si>
   <si>
     <t>Outpat.VExam.Comments</t>
@@ -2229,7 +2229,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="130.3515625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="128.81640625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3179" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3179" uniqueCount="597">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1313,6 +1313,10 @@
     <t>Observation.interpretation.extension.id</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>Observation.interpretation.extension:11179-permitted-value-conceptmap.extension</t>
   </si>
   <si>
@@ -1359,13 +1363,17 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ConceptMap/CMVFExamResultInterpretation</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ext-1
+</t>
   </si>
   <si>
     <t>Observation.interpretation.coding</t>
@@ -7469,7 +7477,7 @@
         <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>222</v>
+        <v>97</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>223</v>
@@ -7535,7 +7543,7 @@
         <v>95</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>84</v>
+        <v>415</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>84</v>
@@ -7567,10 +7575,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7596,10 +7604,10 @@
         <v>141</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7691,10 +7699,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7720,13 +7728,13 @@
         <v>109</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7734,7 +7742,7 @@
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>84</v>
@@ -7776,7 +7784,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>95</v>
@@ -7817,10 +7825,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7843,13 +7851,13 @@
         <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7861,7 +7869,7 @@
         <v>84</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>84</v>
@@ -7900,7 +7908,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7909,7 +7917,7 @@
         <v>95</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>84</v>
+        <v>434</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>107</v>
@@ -7941,10 +7949,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8069,10 +8077,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8197,10 +8205,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8223,19 +8231,19 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8284,7 +8292,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8311,10 +8319,10 @@
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8325,10 +8333,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8449,10 +8457,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8575,10 +8583,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8601,16 +8609,16 @@
         <v>96</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8660,7 +8668,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8690,7 +8698,7 @@
         <v>138</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8701,10 +8709,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8730,10 +8738,10 @@
         <v>295</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8784,7 +8792,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8814,7 +8822,7 @@
         <v>138</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8825,10 +8833,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8851,13 +8859,13 @@
         <v>96</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8908,7 +8916,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>95</v>
@@ -8923,10 +8931,10 @@
         <v>107</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>84</v>
@@ -8938,7 +8946,7 @@
         <v>138</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -8949,10 +8957,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8978,13 +8986,13 @@
         <v>195</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -9013,10 +9021,10 @@
         <v>212</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>84</v>
@@ -9034,7 +9042,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9058,27 +9066,27 @@
         <v>84</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9104,16 +9112,16 @@
         <v>195</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -9141,10 +9149,10 @@
         <v>212</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>84</v>
@@ -9162,7 +9170,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9189,10 +9197,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9203,10 +9211,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9229,16 +9237,16 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9288,7 +9296,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9312,27 +9320,27 @@
         <v>84</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9355,16 +9363,16 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9414,7 +9422,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9438,27 +9446,27 @@
         <v>84</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR57" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9481,19 +9489,19 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9542,7 +9550,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9554,7 +9562,7 @@
         <v>84</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>84</v>
@@ -9569,10 +9577,10 @@
         <v>84</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9583,10 +9591,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9707,10 +9715,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9833,14 +9841,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9862,10 +9870,10 @@
         <v>141</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>144</v>
@@ -9920,7 +9928,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9961,10 +9969,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9987,13 +9995,13 @@
         <v>84</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10044,7 +10052,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10053,7 +10061,7 @@
         <v>95</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>107</v>
@@ -10071,10 +10079,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10085,10 +10093,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10111,13 +10119,13 @@
         <v>84</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -10168,7 +10176,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10177,7 +10185,7 @@
         <v>95</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>107</v>
@@ -10195,10 +10203,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10209,10 +10217,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10238,16 +10246,16 @@
         <v>195</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10275,10 +10283,10 @@
         <v>119</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>84</v>
@@ -10296,7 +10304,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10320,10 +10328,10 @@
         <v>84</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>403</v>
@@ -10337,10 +10345,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10366,16 +10374,16 @@
         <v>195</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -10403,10 +10411,10 @@
         <v>212</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>84</v>
@@ -10424,7 +10432,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10448,10 +10456,10 @@
         <v>84</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>403</v>
@@ -10465,10 +10473,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10491,17 +10499,17 @@
         <v>84</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
@@ -10550,7 +10558,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10580,7 +10588,7 @@
         <v>84</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -10591,10 +10599,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10620,10 +10628,10 @@
         <v>222</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10674,7 +10682,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10701,10 +10709,10 @@
         <v>84</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
@@ -10715,10 +10723,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10741,16 +10749,16 @@
         <v>96</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10800,7 +10808,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -10827,10 +10835,10 @@
         <v>84</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
@@ -10841,10 +10849,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10867,16 +10875,16 @@
         <v>96</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10926,7 +10934,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -10953,10 +10961,10 @@
         <v>84</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -10967,10 +10975,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10993,19 +11001,19 @@
         <v>96</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -11054,7 +11062,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11081,10 +11089,10 @@
         <v>84</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11095,10 +11103,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11219,10 +11227,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11345,14 +11353,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -11374,10 +11382,10 @@
         <v>141</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>144</v>
@@ -11432,7 +11440,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11473,10 +11481,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11502,13 +11510,13 @@
         <v>195</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="O74" t="s" s="2">
         <v>211</v>
@@ -11560,7 +11568,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>95</v>
@@ -11584,7 +11592,7 @@
         <v>84</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>217</v>
@@ -11601,10 +11609,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11630,13 +11638,13 @@
         <v>317</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="M75" t="s" s="2">
         <v>319</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="O75" t="s" s="2">
         <v>321</v>
@@ -11688,7 +11696,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -11712,7 +11720,7 @@
         <v>84</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>324</v>
@@ -11729,10 +11737,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11758,13 +11766,13 @@
         <v>195</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="O76" t="s" s="2">
         <v>385</v>
@@ -11816,7 +11824,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -11857,10 +11865,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11944,7 +11952,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -11985,10 +11993,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12014,16 +12022,16 @@
         <v>85</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>84</v>
@@ -12072,7 +12080,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12099,10 +12107,10 @@
         <v>84</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3179" uniqueCount="597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3179" uniqueCount="600">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -772,6 +772,9 @@
     <t>1581: source value from V EXAM - EXAM &gt; EXAM - CODE MAPPINGS &gt; CODE MAPPINGS (9000010.13-.01 &gt; 9999999.15-210&gt;9999999.18)</t>
   </si>
   <si>
+    <t>Outpat.VExam.ExamIEN</t>
+  </si>
+  <si>
     <t>C*E.1-8, C*E.10-22</t>
   </si>
   <si>
@@ -824,6 +827,9 @@
     <t>1582: reference from V EXAM - PATIENT NAME &gt; PATIENT/IHS - NAME (9000010.13-.02 &gt; 9000001-.01)</t>
   </si>
   <si>
+    <t>Outpat.VExam.PatientIEN</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -881,7 +887,7 @@
     <t>1583: reference from V EXAM - VISIT (9000010.13-.03)</t>
   </si>
   <si>
-    <t>Outpat.VExam.VisitDateTime</t>
+    <t>Outpat.VExam.VisitDateTime,Outpat.VExam.VisitIEN</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -993,6 +999,9 @@
   </si>
   <si>
     <t>1590: reference from V EXAM - ENCOUNTER PROVIDER (9000010.13-1204)</t>
+  </si>
+  <si>
+    <t>Outpat.VExam.EncounterProviderIEN</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -2238,7 +2247,7 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="128.81640625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="49.3203125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
@@ -4634,7 +4643,7 @@
         <v>240</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>84</v>
+        <v>241</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>84</v>
@@ -4643,10 +4652,10 @@
         <v>84</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>84</v>
@@ -4657,10 +4666,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4686,16 +4695,16 @@
         <v>222</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>84</v>
@@ -4744,7 +4753,7 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -4771,10 +4780,10 @@
         <v>84</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>84</v>
@@ -4785,10 +4794,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4811,19 +4820,19 @@
         <v>96</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>84</v>
@@ -4872,7 +4881,7 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -4887,25 +4896,25 @@
         <v>107</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>84</v>
+        <v>259</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AR21" t="s" s="2">
         <v>84</v>
@@ -4913,10 +4922,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4939,16 +4948,16 @@
         <v>96</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4998,7 +5007,7 @@
         <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -5028,10 +5037,10 @@
         <v>217</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>84</v>
@@ -5039,14 +5048,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5065,19 +5074,19 @@
         <v>96</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>84</v>
@@ -5126,7 +5135,7 @@
         <v>84</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -5141,25 +5150,25 @@
         <v>107</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -5167,14 +5176,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5193,19 +5202,19 @@
         <v>96</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
@@ -5242,7 +5251,7 @@
         <v>84</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AC24" s="2"/>
       <c r="AD24" t="s" s="2">
@@ -5252,7 +5261,7 @@
         <v>231</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5273,19 +5282,19 @@
         <v>84</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>84</v>
@@ -5293,16 +5302,16 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5321,19 +5330,19 @@
         <v>96</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5382,7 +5391,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5397,25 +5406,25 @@
         <v>107</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AR25" t="s" s="2">
         <v>84</v>
@@ -5423,10 +5432,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5449,16 +5458,16 @@
         <v>96</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5508,7 +5517,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5535,13 +5544,13 @@
         <v>84</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AR26" t="s" s="2">
         <v>84</v>
@@ -5549,10 +5558,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5575,17 +5584,17 @@
         <v>96</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>84</v>
@@ -5634,7 +5643,7 @@
         <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5649,25 +5658,25 @@
         <v>107</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>84</v>
+        <v>314</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>84</v>
@@ -5675,10 +5684,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5701,19 +5710,19 @@
         <v>96</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5750,7 +5759,7 @@
         <v>84</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
@@ -5760,7 +5769,7 @@
         <v>231</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5769,7 +5778,7 @@
         <v>95</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>107</v>
@@ -5784,30 +5793,30 @@
         <v>84</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>84</v>
@@ -5829,19 +5838,19 @@
         <v>96</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5890,7 +5899,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5899,13 +5908,13 @@
         <v>95</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>84</v>
@@ -5914,27 +5923,27 @@
         <v>84</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6055,10 +6064,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6181,10 +6190,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6207,19 +6216,19 @@
         <v>96</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6268,7 +6277,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6283,7 +6292,7 @@
         <v>107</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>84</v>
@@ -6295,10 +6304,10 @@
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
@@ -6309,10 +6318,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6338,20 +6347,20 @@
         <v>115</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q33" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="R33" t="s" s="2">
         <v>84</v>
@@ -6375,10 +6384,10 @@
         <v>185</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>84</v>
@@ -6396,7 +6405,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6423,10 +6432,10 @@
         <v>84</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -6437,10 +6446,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6466,14 +6475,14 @@
         <v>222</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6522,7 +6531,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6549,10 +6558,10 @@
         <v>84</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
@@ -6563,10 +6572,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6592,14 +6601,14 @@
         <v>109</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6648,7 +6657,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6657,7 +6666,7 @@
         <v>95</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>107</v>
@@ -6675,10 +6684,10 @@
         <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -6689,10 +6698,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6718,16 +6727,16 @@
         <v>115</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6776,7 +6785,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6803,10 +6812,10 @@
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -6817,10 +6826,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6846,16 +6855,16 @@
         <v>195</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6880,13 +6889,13 @@
         <v>84</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>84</v>
@@ -6904,7 +6913,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6913,7 +6922,7 @@
         <v>95</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>107</v>
@@ -6934,7 +6943,7 @@
         <v>138</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -6945,14 +6954,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6974,16 +6983,16 @@
         <v>195</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -7008,13 +7017,13 @@
         <v>84</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>84</v>
@@ -7032,7 +7041,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7047,36 +7056,36 @@
         <v>107</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7197,10 +7206,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7323,13 +7332,13 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>84</v>
@@ -7351,16 +7360,16 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7451,10 +7460,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7543,7 +7552,7 @@
         <v>95</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>84</v>
@@ -7575,10 +7584,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7604,10 +7613,10 @@
         <v>141</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7699,10 +7708,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7728,13 +7737,13 @@
         <v>109</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7742,7 +7751,7 @@
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>84</v>
@@ -7784,7 +7793,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>95</v>
@@ -7825,10 +7834,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7851,13 +7860,13 @@
         <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7869,7 +7878,7 @@
         <v>84</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>84</v>
@@ -7908,7 +7917,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7917,7 +7926,7 @@
         <v>95</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>107</v>
@@ -7949,10 +7958,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8063,10 +8072,10 @@
         <v>84</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -8077,10 +8086,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8106,16 +8115,16 @@
         <v>222</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
@@ -8164,7 +8173,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8191,10 +8200,10 @@
         <v>84</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8205,10 +8214,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8231,19 +8240,19 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8292,7 +8301,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8319,10 +8328,10 @@
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8333,10 +8342,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8457,10 +8466,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8583,10 +8592,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8609,16 +8618,16 @@
         <v>96</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8668,7 +8677,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8698,7 +8707,7 @@
         <v>138</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8709,10 +8718,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8735,13 +8744,13 @@
         <v>96</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8792,7 +8801,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8822,7 +8831,7 @@
         <v>138</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8833,10 +8842,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8859,13 +8868,13 @@
         <v>96</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8916,7 +8925,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>95</v>
@@ -8931,10 +8940,10 @@
         <v>107</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>84</v>
@@ -8946,7 +8955,7 @@
         <v>138</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -8957,10 +8966,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8986,13 +8995,13 @@
         <v>195</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -9021,10 +9030,10 @@
         <v>212</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>84</v>
@@ -9042,7 +9051,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9066,27 +9075,27 @@
         <v>84</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9112,16 +9121,16 @@
         <v>195</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -9149,10 +9158,10 @@
         <v>212</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>84</v>
@@ -9170,7 +9179,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9197,10 +9206,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9211,10 +9220,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9237,16 +9246,16 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9296,7 +9305,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9320,27 +9329,27 @@
         <v>84</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9363,16 +9372,16 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9422,7 +9431,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9446,27 +9455,27 @@
         <v>84</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR57" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9489,19 +9498,19 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9550,7 +9559,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9562,7 +9571,7 @@
         <v>84</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>84</v>
@@ -9577,10 +9586,10 @@
         <v>84</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9591,10 +9600,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9715,10 +9724,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9841,14 +9850,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9870,10 +9879,10 @@
         <v>141</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>144</v>
@@ -9928,7 +9937,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9969,10 +9978,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9995,13 +10004,13 @@
         <v>84</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10052,7 +10061,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10061,7 +10070,7 @@
         <v>95</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>107</v>
@@ -10079,10 +10088,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10093,10 +10102,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10119,13 +10128,13 @@
         <v>84</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -10176,7 +10185,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10185,7 +10194,7 @@
         <v>95</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>107</v>
@@ -10203,10 +10212,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10217,10 +10226,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10246,16 +10255,16 @@
         <v>195</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10283,10 +10292,10 @@
         <v>119</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>84</v>
@@ -10304,7 +10313,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10328,13 +10337,13 @@
         <v>84</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10345,10 +10354,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10374,16 +10383,16 @@
         <v>195</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -10411,10 +10420,10 @@
         <v>212</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>84</v>
@@ -10432,7 +10441,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10456,13 +10465,13 @@
         <v>84</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -10473,10 +10482,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10499,17 +10508,17 @@
         <v>84</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
@@ -10558,7 +10567,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10588,7 +10597,7 @@
         <v>84</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -10599,10 +10608,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10628,10 +10637,10 @@
         <v>222</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10682,7 +10691,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10709,10 +10718,10 @@
         <v>84</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
@@ -10723,10 +10732,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10749,16 +10758,16 @@
         <v>96</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10808,7 +10817,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -10835,10 +10844,10 @@
         <v>84</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
@@ -10849,10 +10858,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10875,16 +10884,16 @@
         <v>96</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10934,7 +10943,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -10961,10 +10970,10 @@
         <v>84</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -10975,10 +10984,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11001,19 +11010,19 @@
         <v>96</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -11062,7 +11071,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11089,10 +11098,10 @@
         <v>84</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11103,10 +11112,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11227,10 +11236,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11353,14 +11362,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -11382,10 +11391,10 @@
         <v>141</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>144</v>
@@ -11440,7 +11449,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11481,10 +11490,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11510,13 +11519,13 @@
         <v>195</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="O74" t="s" s="2">
         <v>211</v>
@@ -11568,7 +11577,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>95</v>
@@ -11592,7 +11601,7 @@
         <v>84</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>217</v>
@@ -11609,10 +11618,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11635,19 +11644,19 @@
         <v>96</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>84</v>
@@ -11696,7 +11705,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -11720,27 +11729,27 @@
         <v>84</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11766,16 +11775,16 @@
         <v>195</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>84</v>
@@ -11800,13 +11809,13 @@
         <v>84</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>84</v>
@@ -11824,7 +11833,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -11833,7 +11842,7 @@
         <v>95</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>107</v>
@@ -11854,7 +11863,7 @@
         <v>138</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
@@ -11865,14 +11874,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11894,16 +11903,16 @@
         <v>195</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -11928,13 +11937,13 @@
         <v>84</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>84</v>
@@ -11952,7 +11961,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -11976,27 +11985,27 @@
         <v>84</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12022,16 +12031,16 @@
         <v>85</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>84</v>
@@ -12080,7 +12089,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12107,10 +12116,10 @@
         <v>84</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$85</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3179" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3460" uniqueCount="648">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -781,6 +781,139 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
+    <t>Observation.code.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://va.gov/terminology/vistaDefinedTerms/9999999.15</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>1580-1: fixed value = http://va.gov/terminology/vistaDefinedTerms/9999999.15</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>1581-2: source value from V EXAM - EXAM &gt; EXAM - CODE MAPPINGS &gt; CODE MAPPINGS - CODE (9000010.13-.01 &gt; 9999999.15-210&gt;9999999.18-1)</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>1580-3: source value from V EXAM - EXAM &gt; EXAM - PRINT NAME (9000010.13-.01 &gt; 9999999.15-200)</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
     <t>Observation.code.text</t>
   </si>
   <si>
@@ -1061,7 +1194,7 @@
 </t>
   </si>
   <si>
-    <t>1586: source value from V EXAM - UCUM CODE (9000010.13-221)</t>
+    <t>1586: source value from V EXAM - UCUM CODE &gt; UCUM CODES (9000010.13-221 &gt; 757.5-)</t>
   </si>
   <si>
     <t>Observation.value[x]:valueQuantity.id</t>
@@ -1161,6 +1294,12 @@
     <t>Quantity.unit</t>
   </si>
   <si>
+    <t>1586-1: source value from V EXAM - UCUM CODE &gt; UCUM CODES - DESCRIPTION (9000010.13-221 &gt; 757.5-.01)</t>
+  </si>
+  <si>
+    <t>Dim.UCUMCode.DescriptionOfTheUnit</t>
+  </si>
+  <si>
     <t>(see OBX.6 etc.) / CQ.2</t>
   </si>
   <si>
@@ -1211,6 +1350,12 @@
   </si>
   <si>
     <t>Quantity.code</t>
+  </si>
+  <si>
+    <t>1586-2: source value from V EXAM - UCUM CODE &gt; UCUM CODES - UCUM CODE (9000010.13-221 &gt; 757.5-1)</t>
+  </si>
+  <si>
+    <t>Dim.UCUMCode.UCUMCode</t>
   </si>
   <si>
     <t>PQ.code, MO.currency, PQ.translation.code</t>
@@ -2208,7 +2353,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR78"/>
+  <dimension ref="A1:AR85"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="78.4609375" customWidth="true" bestFit="true"/>
@@ -2246,7 +2391,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="128.81640625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="139.59375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="49.3203125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
@@ -4689,23 +4834,19 @@
         <v>84</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K20" t="s" s="2">
         <v>222</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>84</v>
       </c>
@@ -4753,7 +4894,7 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -4765,7 +4906,7 @@
         <v>84</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>84</v>
@@ -4780,10 +4921,10 @@
         <v>84</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>250</v>
+        <v>84</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>84</v>
@@ -4794,46 +4935,44 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>253</v>
+        <v>141</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>254</v>
+        <v>142</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>255</v>
+        <v>228</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>257</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>84</v>
       </c>
@@ -4869,52 +5008,52 @@
         <v>84</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>84</v>
+        <v>229</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>84</v>
+        <v>231</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>258</v>
+        <v>84</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>259</v>
+        <v>84</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>260</v>
+        <v>84</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>261</v>
+        <v>84</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>262</v>
+        <v>226</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>263</v>
+        <v>84</v>
       </c>
       <c r="AR21" t="s" s="2">
         <v>84</v>
@@ -4922,10 +5061,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4936,10 +5075,10 @@
         <v>82</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>84</v>
@@ -4948,18 +5087,20 @@
         <v>96</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>265</v>
+        <v>109</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>266</v>
+        <v>247</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>267</v>
+        <v>248</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>84</v>
       </c>
@@ -4968,7 +5109,7 @@
         <v>84</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>84</v>
+        <v>251</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>84</v>
@@ -5007,13 +5148,13 @@
         <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>84</v>
@@ -5022,7 +5163,7 @@
         <v>107</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>84</v>
+        <v>253</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>84</v>
@@ -5034,13 +5175,13 @@
         <v>84</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>217</v>
+        <v>254</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>263</v>
+        <v>84</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>84</v>
@@ -5048,14 +5189,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>271</v>
+        <v>84</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5065,7 +5206,7 @@
         <v>95</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>84</v>
@@ -5074,20 +5215,18 @@
         <v>96</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>272</v>
+        <v>222</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>84</v>
       </c>
@@ -5135,7 +5274,7 @@
         <v>84</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -5150,25 +5289,25 @@
         <v>107</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>277</v>
+        <v>84</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>278</v>
+        <v>84</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>279</v>
+        <v>84</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>282</v>
+        <v>84</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -5176,14 +5315,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>284</v>
+        <v>84</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5193,7 +5332,7 @@
         <v>95</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>84</v>
@@ -5202,19 +5341,17 @@
         <v>96</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>285</v>
+        <v>115</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>289</v>
+        <v>266</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
@@ -5251,17 +5388,19 @@
         <v>84</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="AC24" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>231</v>
+        <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5276,25 +5415,25 @@
         <v>107</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>84</v>
+        <v>268</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>84</v>
+        <v>241</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>291</v>
+        <v>84</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>292</v>
+        <v>269</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>294</v>
+        <v>84</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>84</v>
@@ -5302,16 +5441,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>295</v>
+        <v>271</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>284</v>
+        <v>84</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5330,19 +5467,17 @@
         <v>96</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>297</v>
+        <v>222</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5391,7 +5526,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -5406,25 +5541,25 @@
         <v>107</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>299</v>
+        <v>241</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>291</v>
+        <v>84</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>294</v>
+        <v>84</v>
       </c>
       <c r="AR25" t="s" s="2">
         <v>84</v>
@@ -5432,10 +5567,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>300</v>
+        <v>279</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>300</v>
+        <v>279</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5458,18 +5593,20 @@
         <v>96</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>301</v>
+        <v>280</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>302</v>
+        <v>281</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>303</v>
+        <v>282</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>84</v>
       </c>
@@ -5517,7 +5654,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5544,13 +5681,13 @@
         <v>84</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>307</v>
+        <v>84</v>
       </c>
       <c r="AR26" t="s" s="2">
         <v>84</v>
@@ -5558,10 +5695,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5572,10 +5709,10 @@
         <v>82</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>84</v>
@@ -5584,17 +5721,19 @@
         <v>96</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>309</v>
+        <v>222</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>310</v>
+        <v>289</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="O27" t="s" s="2">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>84</v>
@@ -5643,13 +5782,13 @@
         <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>84</v>
@@ -5658,25 +5797,25 @@
         <v>107</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>313</v>
+        <v>84</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>314</v>
+        <v>84</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>315</v>
+        <v>84</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>316</v>
+        <v>294</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>317</v>
+        <v>295</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>318</v>
+        <v>84</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>84</v>
@@ -5684,10 +5823,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>319</v>
+        <v>296</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>319</v>
+        <v>296</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5701,7 +5840,7 @@
         <v>95</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>84</v>
@@ -5710,19 +5849,19 @@
         <v>96</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>320</v>
+        <v>297</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>321</v>
+        <v>298</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>322</v>
+        <v>299</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>323</v>
+        <v>300</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5759,17 +5898,19 @@
         <v>84</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="AC28" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>231</v>
+        <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>319</v>
+        <v>296</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5778,46 +5919,44 @@
         <v>95</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>325</v>
+        <v>84</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>84</v>
+        <v>302</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>84</v>
+        <v>303</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>84</v>
+        <v>304</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>326</v>
+        <v>84</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>327</v>
+        <v>305</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>328</v>
+        <v>306</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>84</v>
+        <v>307</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>329</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>84</v>
       </c>
@@ -5826,10 +5965,10 @@
         <v>82</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>84</v>
@@ -5838,20 +5977,18 @@
         <v>96</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>332</v>
+        <v>309</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>84</v>
       </c>
@@ -5899,22 +6036,22 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>325</v>
+        <v>84</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>333</v>
+        <v>84</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>84</v>
@@ -5923,31 +6060,31 @@
         <v>84</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>326</v>
+        <v>84</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>327</v>
+        <v>217</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>84</v>
+        <v>307</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>329</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>334</v>
+        <v>314</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>335</v>
+        <v>314</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>84</v>
+        <v>315</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5957,25 +6094,29 @@
         <v>95</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>222</v>
+        <v>316</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>223</v>
+        <v>317</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>84</v>
       </c>
@@ -6023,7 +6164,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>225</v>
+        <v>314</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6035,28 +6176,28 @@
         <v>84</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>84</v>
+        <v>321</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>84</v>
+        <v>322</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>84</v>
+        <v>323</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>84</v>
+        <v>324</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>226</v>
+        <v>325</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>84</v>
+        <v>326</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>84</v>
@@ -6064,21 +6205,21 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>140</v>
+        <v>328</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>84</v>
@@ -6087,21 +6228,23 @@
         <v>84</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>141</v>
+        <v>329</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>142</v>
+        <v>330</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>228</v>
+        <v>331</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>332</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>84</v>
       </c>
@@ -6137,11 +6280,9 @@
         <v>84</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="AC31" s="2"/>
       <c r="AD31" t="s" s="2">
         <v>84</v>
       </c>
@@ -6149,19 +6290,19 @@
         <v>231</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>232</v>
+        <v>327</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>84</v>
@@ -6170,19 +6311,19 @@
         <v>84</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>84</v>
+        <v>335</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>84</v>
+        <v>336</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>226</v>
+        <v>337</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>84</v>
+        <v>338</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>84</v>
@@ -6190,14 +6331,16 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="C32" s="2"/>
+        <v>327</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="D32" t="s" s="2">
-        <v>84</v>
+        <v>328</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -6216,19 +6359,19 @@
         <v>96</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6277,7 +6420,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6292,25 +6435,25 @@
         <v>107</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>84</v>
+        <v>343</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>84</v>
+        <v>335</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>84</v>
+        <v>338</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>84</v>
@@ -6318,10 +6461,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6338,30 +6481,28 @@
         <v>84</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>115</v>
+        <v>345</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" t="s" s="2">
-        <v>353</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q33" t="s" s="2">
-        <v>354</v>
-      </c>
+      <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
         <v>84</v>
       </c>
@@ -6381,13 +6522,13 @@
         <v>84</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>185</v>
+        <v>84</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>355</v>
+        <v>84</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>356</v>
+        <v>84</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>84</v>
@@ -6405,7 +6546,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6432,13 +6573,13 @@
         <v>84</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>84</v>
+        <v>351</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>84</v>
@@ -6446,10 +6587,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6460,10 +6601,10 @@
         <v>82</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>84</v>
@@ -6472,17 +6613,17 @@
         <v>96</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>222</v>
+        <v>353</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6531,13 +6672,13 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>84</v>
@@ -6546,25 +6687,25 @@
         <v>107</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>84</v>
+        <v>357</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>84</v>
+        <v>358</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>84</v>
+        <v>359</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>84</v>
+        <v>362</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>84</v>
@@ -6572,10 +6713,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6598,17 +6739,19 @@
         <v>96</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>109</v>
+        <v>364</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>367</v>
+      </c>
       <c r="O35" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6645,19 +6788,17 @@
         <v>84</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="AC35" s="2"/>
       <c r="AD35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>84</v>
+        <v>231</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6666,7 +6807,7 @@
         <v>95</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>107</v>
@@ -6681,29 +6822,31 @@
         <v>84</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>84</v>
+        <v>370</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>84</v>
+        <v>373</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="D36" t="s" s="2">
         <v>84</v>
       </c>
@@ -6715,7 +6858,7 @@
         <v>95</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>84</v>
@@ -6724,19 +6867,19 @@
         <v>96</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>115</v>
+        <v>376</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6785,7 +6928,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6794,13 +6937,13 @@
         <v>95</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>84</v>
+        <v>369</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>84</v>
+        <v>377</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>84</v>
@@ -6809,27 +6952,27 @@
         <v>84</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>84</v>
+        <v>370</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>84</v>
+        <v>373</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6852,20 +6995,16 @@
         <v>84</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>385</v>
+        <v>223</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>84</v>
       </c>
@@ -6889,13 +7028,13 @@
         <v>84</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>389</v>
+        <v>84</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>390</v>
+        <v>84</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>391</v>
+        <v>84</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>84</v>
@@ -6913,7 +7052,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>384</v>
+        <v>225</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6922,10 +7061,10 @@
         <v>95</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>392</v>
+        <v>84</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>84</v>
@@ -6940,10 +7079,10 @@
         <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>393</v>
+        <v>226</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -6954,14 +7093,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>395</v>
+        <v>140</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6971,7 +7110,7 @@
         <v>83</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>84</v>
@@ -6980,20 +7119,18 @@
         <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>195</v>
+        <v>141</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>396</v>
+        <v>142</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>397</v>
+        <v>228</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>84</v>
       </c>
@@ -7017,31 +7154,31 @@
         <v>84</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>389</v>
+        <v>84</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>400</v>
+        <v>84</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>401</v>
+        <v>84</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>84</v>
+        <v>229</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>84</v>
+        <v>231</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>394</v>
+        <v>232</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7053,39 +7190,39 @@
         <v>84</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>402</v>
+        <v>84</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>403</v>
+        <v>84</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>404</v>
+        <v>84</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>405</v>
+        <v>84</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>406</v>
+        <v>226</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>407</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>408</v>
+        <v>382</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>408</v>
+        <v>383</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7099,25 +7236,29 @@
         <v>95</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>222</v>
+        <v>384</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>223</v>
+        <v>385</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>386</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
       </c>
@@ -7165,7 +7306,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>225</v>
+        <v>389</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7177,10 +7318,10 @@
         <v>84</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>84</v>
+        <v>390</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>84</v>
@@ -7192,10 +7333,10 @@
         <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>84</v>
+        <v>391</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>226</v>
+        <v>392</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -7206,48 +7347,50 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>409</v>
+        <v>393</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>141</v>
+        <v>115</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>142</v>
+        <v>395</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q40" s="2"/>
+      <c r="Q40" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="R40" t="s" s="2">
         <v>84</v>
       </c>
@@ -7267,43 +7410,43 @@
         <v>84</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>84</v>
+        <v>185</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>84</v>
+        <v>399</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>84</v>
+        <v>400</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>229</v>
+        <v>84</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>230</v>
+        <v>84</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>231</v>
+        <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>232</v>
+        <v>401</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>84</v>
@@ -7318,10 +7461,10 @@
         <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>84</v>
+        <v>402</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>226</v>
+        <v>403</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -7332,14 +7475,12 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
         <v>84</v>
       </c>
@@ -7351,27 +7492,27 @@
         <v>95</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>412</v>
+        <v>222</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>407</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>408</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
       </c>
@@ -7419,25 +7560,25 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>232</v>
+        <v>409</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>84</v>
+        <v>410</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>84</v>
+        <v>411</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>84</v>
@@ -7446,10 +7587,10 @@
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>138</v>
+        <v>412</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>138</v>
+        <v>413</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7460,10 +7601,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7483,19 +7624,21 @@
         <v>84</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>223</v>
+        <v>416</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>224</v>
+        <v>417</v>
       </c>
       <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>418</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>84</v>
       </c>
@@ -7543,7 +7686,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>225</v>
+        <v>419</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7552,10 +7695,10 @@
         <v>95</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>84</v>
@@ -7570,10 +7713,10 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>84</v>
+        <v>412</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>226</v>
+        <v>421</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7584,10 +7727,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7598,28 +7741,32 @@
         <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>141</v>
+        <v>115</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>425</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>427</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
       </c>
@@ -7655,37 +7802,37 @@
         <v>84</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>229</v>
+        <v>84</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>230</v>
+        <v>84</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>231</v>
+        <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>232</v>
+        <v>428</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>84</v>
+        <v>429</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>84</v>
+        <v>430</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>84</v>
@@ -7694,10 +7841,10 @@
         <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>84</v>
+        <v>412</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>84</v>
+        <v>431</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -7708,10 +7855,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7719,7 +7866,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>95</v>
@@ -7734,24 +7881,26 @@
         <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>109</v>
+        <v>195</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>428</v>
+        <v>84</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>84</v>
@@ -7769,13 +7918,13 @@
         <v>84</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>84</v>
+        <v>437</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>84</v>
+        <v>438</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>84</v>
+        <v>439</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>84</v>
@@ -7793,19 +7942,19 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>84</v>
+        <v>440</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>84</v>
@@ -7820,10 +7969,10 @@
         <v>84</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>138</v>
+        <v>441</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7834,24 +7983,24 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>84</v>
+        <v>443</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>84</v>
@@ -7860,16 +8009,20 @@
         <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>432</v>
+        <v>195</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>447</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
       </c>
@@ -7878,7 +8031,7 @@
         <v>84</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>435</v>
+        <v>84</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>84</v>
@@ -7893,13 +8046,13 @@
         <v>84</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>84</v>
+        <v>437</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>84</v>
+        <v>448</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>84</v>
+        <v>449</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
@@ -7917,51 +8070,51 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>437</v>
+        <v>84</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>84</v>
+        <v>450</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>84</v>
+        <v>451</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>84</v>
+        <v>452</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>84</v>
+        <v>453</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>138</v>
+        <v>454</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>84</v>
+        <v>455</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7972,7 +8125,7 @@
         <v>82</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>84</v>
@@ -7981,23 +8134,19 @@
         <v>84</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>84</v>
       </c>
@@ -8045,19 +8194,19 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>84</v>
@@ -8072,10 +8221,10 @@
         <v>84</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>242</v>
+        <v>84</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -8086,21 +8235,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>84</v>
@@ -8109,23 +8258,21 @@
         <v>84</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>222</v>
+        <v>141</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>245</v>
+        <v>142</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>84</v>
       </c>
@@ -8161,31 +8308,31 @@
         <v>84</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>84</v>
+        <v>229</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>84</v>
+        <v>231</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>84</v>
@@ -8200,10 +8347,10 @@
         <v>84</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>250</v>
+        <v>84</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8214,12 +8361,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="C48" s="2"/>
+        <v>457</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>459</v>
+      </c>
       <c r="D48" t="s" s="2">
         <v>84</v>
       </c>
@@ -8228,7 +8377,7 @@
         <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>84</v>
@@ -8240,20 +8389,18 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>441</v>
+        <v>460</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>445</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>84</v>
       </c>
@@ -8301,7 +8448,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>440</v>
+        <v>232</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8313,7 +8460,7 @@
         <v>84</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>84</v>
@@ -8328,10 +8475,10 @@
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>446</v>
+        <v>138</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>447</v>
+        <v>138</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8342,10 +8489,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>448</v>
+        <v>464</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>448</v>
+        <v>465</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8368,7 +8515,7 @@
         <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>222</v>
+        <v>97</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>223</v>
@@ -8434,7 +8581,7 @@
         <v>95</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>84</v>
+        <v>466</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>84</v>
@@ -8466,21 +8613,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>449</v>
+        <v>467</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>449</v>
+        <v>468</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>84</v>
@@ -8495,14 +8642,12 @@
         <v>141</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>142</v>
+        <v>469</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8581,7 +8726,7 @@
         <v>84</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>226</v>
+        <v>84</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8592,10 +8737,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>450</v>
+        <v>471</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>450</v>
+        <v>472</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8603,7 +8748,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>95</v>
@@ -8615,19 +8760,19 @@
         <v>84</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>451</v>
+        <v>109</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>452</v>
+        <v>473</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>453</v>
+        <v>474</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>454</v>
+        <v>475</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8635,7 +8780,7 @@
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>84</v>
+        <v>476</v>
       </c>
       <c r="S51" t="s" s="2">
         <v>84</v>
@@ -8677,10 +8822,10 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>455</v>
+        <v>477</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>95</v>
@@ -8689,7 +8834,7 @@
         <v>84</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>84</v>
@@ -8704,10 +8849,10 @@
         <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8718,10 +8863,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>457</v>
+        <v>478</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>457</v>
+        <v>479</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8729,7 +8874,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>95</v>
@@ -8741,16 +8886,16 @@
         <v>84</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>297</v>
+        <v>480</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>458</v>
+        <v>481</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>459</v>
+        <v>482</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8762,7 +8907,7 @@
         <v>84</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>84</v>
+        <v>483</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>84</v>
@@ -8801,7 +8946,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>460</v>
+        <v>484</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8810,7 +8955,7 @@
         <v>95</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>84</v>
+        <v>485</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>107</v>
@@ -8828,10 +8973,10 @@
         <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP52" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8842,10 +8987,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>462</v>
+        <v>486</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>462</v>
+        <v>486</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8853,13 +8998,13 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>84</v>
@@ -8868,16 +9013,20 @@
         <v>96</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>463</v>
+        <v>234</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>464</v>
+        <v>235</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
       </c>
@@ -8925,13 +9074,13 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>466</v>
+        <v>239</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>84</v>
@@ -8940,10 +9089,10 @@
         <v>107</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>467</v>
+        <v>84</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>468</v>
+        <v>84</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>84</v>
@@ -8952,10 +9101,10 @@
         <v>84</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>138</v>
+        <v>242</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>469</v>
+        <v>243</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -8966,10 +9115,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>470</v>
+        <v>487</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>470</v>
+        <v>487</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8989,21 +9138,23 @@
         <v>84</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>471</v>
+        <v>289</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>472</v>
+        <v>290</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
       </c>
@@ -9027,13 +9178,13 @@
         <v>84</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>212</v>
+        <v>84</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>474</v>
+        <v>84</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>475</v>
+        <v>84</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>84</v>
@@ -9051,7 +9202,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>470</v>
+        <v>293</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9075,27 +9226,27 @@
         <v>84</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>476</v>
+        <v>84</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>477</v>
+        <v>294</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>478</v>
+        <v>295</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>479</v>
+        <v>84</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9106,7 +9257,7 @@
         <v>82</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>84</v>
@@ -9118,19 +9269,19 @@
         <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>195</v>
+        <v>489</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -9155,13 +9306,13 @@
         <v>84</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>212</v>
+        <v>84</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>485</v>
+        <v>84</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>486</v>
+        <v>84</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>84</v>
@@ -9179,13 +9330,13 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>84</v>
@@ -9206,10 +9357,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9220,10 +9371,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9246,17 +9397,15 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>490</v>
+        <v>222</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>491</v>
+        <v>223</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>493</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>84</v>
@@ -9305,7 +9454,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>489</v>
+        <v>225</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9317,7 +9466,7 @@
         <v>84</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>84</v>
@@ -9329,38 +9478,38 @@
         <v>84</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>494</v>
+        <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>495</v>
+        <v>84</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>496</v>
+        <v>226</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>497</v>
+        <v>84</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>84</v>
@@ -9372,16 +9521,16 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>499</v>
+        <v>141</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>500</v>
+        <v>142</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>501</v>
+        <v>228</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>502</v>
+        <v>144</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9419,31 +9568,31 @@
         <v>84</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>84</v>
+        <v>229</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>84</v>
+        <v>231</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>498</v>
+        <v>232</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>84</v>
@@ -9455,27 +9604,27 @@
         <v>84</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>503</v>
+        <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>504</v>
+        <v>84</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>505</v>
+        <v>226</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR57" t="s" s="2">
-        <v>506</v>
+        <v>84</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9486,7 +9635,7 @@
         <v>82</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>84</v>
@@ -9495,23 +9644,21 @@
         <v>84</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>512</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>84</v>
       </c>
@@ -9559,19 +9706,19 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>513</v>
+        <v>107</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>84</v>
@@ -9586,10 +9733,10 @@
         <v>84</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>514</v>
+        <v>138</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>515</v>
+        <v>504</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9600,10 +9747,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9623,16 +9770,16 @@
         <v>84</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>222</v>
+        <v>341</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>223</v>
+        <v>506</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>224</v>
+        <v>507</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9683,7 +9830,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>225</v>
+        <v>508</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9695,7 +9842,7 @@
         <v>84</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>84</v>
@@ -9710,10 +9857,10 @@
         <v>84</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>226</v>
+        <v>509</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9724,43 +9871,41 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>141</v>
+        <v>511</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>142</v>
+        <v>512</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>513</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -9809,25 +9954,25 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>232</v>
+        <v>514</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>84</v>
+        <v>515</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>84</v>
+        <v>516</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>84</v>
@@ -9836,10 +9981,10 @@
         <v>84</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>226</v>
+        <v>517</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9857,39 +10002,37 @@
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>519</v>
+        <v>84</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>141</v>
+        <v>195</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="N61" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>84</v>
       </c>
@@ -9913,13 +10056,13 @@
         <v>84</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>84</v>
+        <v>212</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>84</v>
+        <v>522</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>84</v>
+        <v>523</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>84</v>
@@ -9937,19 +10080,19 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>84</v>
@@ -9961,27 +10104,27 @@
         <v>84</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>84</v>
+        <v>524</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>84</v>
+        <v>525</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>138</v>
+        <v>526</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR61" t="s" s="2">
-        <v>84</v>
+        <v>527</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10004,16 +10147,20 @@
         <v>84</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>524</v>
+        <v>195</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>530</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>532</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
       </c>
@@ -10037,13 +10184,13 @@
         <v>84</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>84</v>
+        <v>212</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>84</v>
+        <v>533</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>84</v>
+        <v>534</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>84</v>
@@ -10061,7 +10208,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10070,7 +10217,7 @@
         <v>95</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>527</v>
+        <v>84</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>107</v>
@@ -10088,10 +10235,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10102,10 +10249,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10128,15 +10275,17 @@
         <v>84</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>524</v>
+        <v>538</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>540</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>541</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -10185,7 +10334,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10194,7 +10343,7 @@
         <v>95</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>527</v>
+        <v>84</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>107</v>
@@ -10209,27 +10358,27 @@
         <v>84</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>84</v>
+        <v>542</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>528</v>
+        <v>543</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>533</v>
+        <v>544</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR63" t="s" s="2">
-        <v>84</v>
+        <v>545</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10252,20 +10401,18 @@
         <v>84</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>195</v>
+        <v>547</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>535</v>
+        <v>548</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>536</v>
+        <v>549</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>538</v>
-      </c>
+        <v>550</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>84</v>
       </c>
@@ -10289,13 +10436,13 @@
         <v>84</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>539</v>
+        <v>84</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>540</v>
+        <v>84</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>84</v>
@@ -10313,7 +10460,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10337,27 +10484,27 @@
         <v>84</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>541</v>
+        <v>551</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>406</v>
+        <v>553</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR64" t="s" s="2">
-        <v>84</v>
+        <v>554</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10380,19 +10527,19 @@
         <v>84</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>195</v>
+        <v>556</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>544</v>
+        <v>557</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>545</v>
+        <v>558</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>546</v>
+        <v>559</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>547</v>
+        <v>560</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -10417,13 +10564,13 @@
         <v>84</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>212</v>
+        <v>84</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>548</v>
+        <v>84</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>549</v>
+        <v>84</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>84</v>
@@ -10441,7 +10588,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10453,7 +10600,7 @@
         <v>84</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>107</v>
+        <v>561</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>84</v>
@@ -10465,13 +10612,13 @@
         <v>84</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>541</v>
+        <v>84</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>542</v>
+        <v>562</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>406</v>
+        <v>563</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -10482,10 +10629,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>550</v>
+        <v>564</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>550</v>
+        <v>564</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10508,18 +10655,16 @@
         <v>84</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>551</v>
+        <v>222</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>552</v>
+        <v>223</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>553</v>
+        <v>224</v>
       </c>
       <c r="N66" s="2"/>
-      <c r="O66" t="s" s="2">
-        <v>554</v>
-      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>84</v>
       </c>
@@ -10567,7 +10712,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>550</v>
+        <v>225</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10579,7 +10724,7 @@
         <v>84</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>84</v>
@@ -10597,7 +10742,7 @@
         <v>84</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>555</v>
+        <v>226</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -10608,21 +10753,21 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>84</v>
@@ -10634,15 +10779,17 @@
         <v>84</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>222</v>
+        <v>141</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>557</v>
+        <v>142</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>84</v>
@@ -10691,19 +10838,19 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>556</v>
+        <v>232</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>84</v>
@@ -10718,10 +10865,10 @@
         <v>84</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>528</v>
+        <v>84</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>559</v>
+        <v>226</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
@@ -10732,14 +10879,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>84</v>
+        <v>567</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10752,24 +10899,26 @@
         <v>84</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="J68" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>561</v>
+        <v>141</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>84</v>
       </c>
@@ -10817,7 +10966,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -10829,7 +10978,7 @@
         <v>84</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>84</v>
@@ -10844,10 +10993,10 @@
         <v>84</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>565</v>
+        <v>84</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>566</v>
+        <v>138</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
@@ -10858,10 +11007,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10872,7 +11021,7 @@
         <v>82</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>84</v>
@@ -10881,20 +11030,18 @@
         <v>84</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>571</v>
-      </c>
+        <v>574</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>84</v>
@@ -10943,16 +11090,16 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>84</v>
+        <v>575</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>107</v>
@@ -10970,10 +11117,10 @@
         <v>84</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>565</v>
+        <v>576</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -10984,10 +11131,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10998,7 +11145,7 @@
         <v>82</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>84</v>
@@ -11007,23 +11154,19 @@
         <v>84</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>508</v>
+        <v>572</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>577</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>84</v>
       </c>
@@ -11071,16 +11214,16 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>84</v>
+        <v>575</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>107</v>
@@ -11098,10 +11241,10 @@
         <v>84</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11112,10 +11255,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11138,16 +11281,20 @@
         <v>84</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>222</v>
+        <v>195</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>223</v>
+        <v>583</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+        <v>584</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>586</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
       </c>
@@ -11171,13 +11318,13 @@
         <v>84</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>84</v>
+        <v>587</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>84</v>
+        <v>588</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11195,7 +11342,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>225</v>
+        <v>582</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11207,7 +11354,7 @@
         <v>84</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>84</v>
@@ -11219,13 +11366,13 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>84</v>
+        <v>589</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>84</v>
+        <v>590</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>226</v>
+        <v>454</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
@@ -11236,14 +11383,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>581</v>
+        <v>591</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>581</v>
+        <v>591</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -11262,18 +11409,20 @@
         <v>84</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>141</v>
+        <v>195</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>142</v>
+        <v>592</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>228</v>
+        <v>593</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O72" s="2"/>
+        <v>594</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>595</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
       </c>
@@ -11297,13 +11446,13 @@
         <v>84</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>84</v>
+        <v>212</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>84</v>
+        <v>596</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>84</v>
+        <v>597</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>84</v>
@@ -11321,7 +11470,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>232</v>
+        <v>591</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11333,7 +11482,7 @@
         <v>84</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>84</v>
@@ -11345,13 +11494,13 @@
         <v>84</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>84</v>
+        <v>589</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>84</v>
+        <v>590</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>226</v>
+        <v>454</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
@@ -11362,45 +11511,43 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>582</v>
+        <v>598</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>582</v>
+        <v>598</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>519</v>
+        <v>84</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>141</v>
+        <v>599</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>520</v>
+        <v>600</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>601</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>150</v>
+        <v>602</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>84</v>
@@ -11449,19 +11596,19 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>522</v>
+        <v>598</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>84</v>
@@ -11479,7 +11626,7 @@
         <v>84</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>138</v>
+        <v>603</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
@@ -11490,10 +11637,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>583</v>
+        <v>604</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>583</v>
+        <v>604</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11501,7 +11648,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>95</v>
@@ -11513,23 +11660,19 @@
         <v>84</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>584</v>
+        <v>605</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>606</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>84</v>
       </c>
@@ -11553,13 +11696,13 @@
         <v>84</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>212</v>
+        <v>84</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>213</v>
+        <v>84</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>84</v>
@@ -11577,10 +11720,10 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>583</v>
+        <v>604</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>95</v>
@@ -11601,16 +11744,16 @@
         <v>84</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>587</v>
+        <v>84</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>217</v>
+        <v>576</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>218</v>
+        <v>607</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>219</v>
+        <v>84</v>
       </c>
       <c r="AR74" t="s" s="2">
         <v>84</v>
@@ -11618,10 +11761,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>588</v>
+        <v>608</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>588</v>
+        <v>608</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11632,7 +11775,7 @@
         <v>82</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>84</v>
@@ -11644,20 +11787,18 @@
         <v>96</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>320</v>
+        <v>609</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>589</v>
+        <v>610</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>322</v>
+        <v>611</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>84</v>
       </c>
@@ -11705,13 +11846,13 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>588</v>
+        <v>608</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>84</v>
@@ -11729,27 +11870,27 @@
         <v>84</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>591</v>
+        <v>84</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>327</v>
+        <v>613</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>328</v>
+        <v>614</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>329</v>
+        <v>84</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>592</v>
+        <v>615</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>592</v>
+        <v>615</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11760,7 +11901,7 @@
         <v>82</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>84</v>
@@ -11769,23 +11910,21 @@
         <v>84</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>195</v>
+        <v>616</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>593</v>
+        <v>617</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>594</v>
+        <v>618</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>619</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>84</v>
       </c>
@@ -11809,13 +11948,13 @@
         <v>84</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>389</v>
+        <v>84</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>390</v>
+        <v>84</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>391</v>
+        <v>84</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>84</v>
@@ -11833,16 +11972,16 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>592</v>
+        <v>615</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>392</v>
+        <v>84</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>107</v>
@@ -11860,10 +11999,10 @@
         <v>84</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>138</v>
+        <v>613</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>393</v>
+        <v>620</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
@@ -11874,14 +12013,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>596</v>
+        <v>621</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>596</v>
+        <v>621</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>395</v>
+        <v>84</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11897,22 +12036,22 @@
         <v>84</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>195</v>
+        <v>556</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>396</v>
+        <v>622</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>397</v>
+        <v>623</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>398</v>
+        <v>624</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>399</v>
+        <v>625</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -11937,13 +12076,13 @@
         <v>84</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>389</v>
+        <v>84</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>400</v>
+        <v>84</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>401</v>
+        <v>84</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>84</v>
@@ -11961,7 +12100,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>596</v>
+        <v>621</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -11985,27 +12124,27 @@
         <v>84</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>404</v>
+        <v>84</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>405</v>
+        <v>626</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>406</v>
+        <v>627</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>407</v>
+        <v>84</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>597</v>
+        <v>628</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>597</v>
+        <v>628</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12016,7 +12155,7 @@
         <v>82</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>84</v>
@@ -12028,20 +12167,16 @@
         <v>84</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>85</v>
+        <v>222</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>598</v>
+        <v>223</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>512</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>84</v>
       </c>
@@ -12089,47 +12224,941 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>597</v>
+        <v>225</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH78" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP78" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AQ78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR78" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G79" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="AI78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
+      <c r="H79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP79" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AQ79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR79" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="P80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP80" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AQ80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR80" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="P81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="AK78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="AP78" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="AQ78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR78" t="s" s="2">
+      <c r="AK81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AO81" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AP81" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AQ81" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AR81" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="P82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AP82" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AQ82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR82" t="s" s="2">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="P83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO83" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AP83" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AQ83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR83" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="P84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AP84" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AQ84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR84" t="s" s="2">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="P85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AP85" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AQ85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR85" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR78">
+  <autoFilter ref="A1:AR85">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12139,7 +13168,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI77">
+  <conditionalFormatting sqref="A2:AI84">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$94</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3460" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3824" uniqueCount="672">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -766,27 +766,46 @@
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>1581: source value from V EXAM - EXAM &gt; EXAM - CODE MAPPINGS &gt; CODE MAPPINGS (9000010.13-.01 &gt; 9999999.15-210&gt;9999999.18)</t>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:va-code</t>
+  </si>
+  <si>
+    <t>va-code</t>
+  </si>
+  <si>
+    <t>1580: source value from V EXAM - EXAM &gt; EXAM (9000010.13-.01 &gt; 9999999.15-)</t>
   </si>
   <si>
     <t>Outpat.VExam.ExamIEN</t>
   </si>
   <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
+    <t>Observation.code.coding:va-code.id</t>
   </si>
   <si>
     <t>Observation.code.coding.id</t>
   </si>
   <si>
+    <t>Observation.code.coding:va-code.extension</t>
+  </si>
+  <si>
     <t>Observation.code.coding.extension</t>
   </si>
   <si>
+    <t>Observation.code.coding:va-code.system</t>
+  </si>
+  <si>
     <t>Observation.code.coding.system</t>
   </si>
   <si>
@@ -817,6 +836,9 @@
     <t>./codeSystem</t>
   </si>
   <si>
+    <t>Observation.code.coding:va-code.version</t>
+  </si>
+  <si>
     <t>Observation.code.coding.version</t>
   </si>
   <si>
@@ -838,6 +860,9 @@
     <t>./codeSystemVersion</t>
   </si>
   <si>
+    <t>Observation.code.coding:va-code.code</t>
+  </si>
+  <si>
     <t>Observation.code.coding.code</t>
   </si>
   <si>
@@ -853,7 +878,11 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1581-2: source value from V EXAM - EXAM &gt; EXAM - CODE MAPPINGS &gt; CODE MAPPINGS - CODE (9000010.13-.01 &gt; 9999999.15-210&gt;9999999.18-1)</t>
+    <t>1580-2: source value from V EXAM - EXAM &gt; EXAM - NAME (9000010.13-.01 &gt; 9999999.15-.01)</t>
+  </si>
+  <si>
+    <t>Outpat.VExam.ExamIEN
+Dim.Exam.Exam</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -862,6 +891,9 @@
     <t>./code</t>
   </si>
   <si>
+    <t>Observation.code.coding:va-code.display</t>
+  </si>
+  <si>
     <t>Observation.code.coding.display</t>
   </si>
   <si>
@@ -884,6 +916,9 @@
   </si>
   <si>
     <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:va-code.userSelected</t>
   </si>
   <si>
     <t>Observation.code.coding.userSelected</t>
@@ -914,6 +949,45 @@
     <t>CD.codingRationale</t>
   </si>
   <si>
+    <t>Observation.code.coding:va-sct</t>
+  </si>
+  <si>
+    <t>va-sct</t>
+  </si>
+  <si>
+    <t>1581: source value from V EXAM - EXAM &gt; EXAM - CODE MAPPINGS &gt; CODE MAPPINGS (9000010.13-.01 &gt; 9999999.15-210&gt;9999999.18)</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:va-sct.id</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:va-sct.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:va-sct.system</t>
+  </si>
+  <si>
+    <t>urn:see-termmap-in-mapParameter</t>
+  </si>
+  <si>
+    <t>1581-1: fixed value = urn:see-termmap-in-mapParameter</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:va-sct.version</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:va-sct.code</t>
+  </si>
+  <si>
+    <t>1581-2: source value from V EXAM - EXAM &gt; EXAM - CODE MAPPINGS &gt; CODE MAPPINGS - CODE (9000010.13-.01 &gt; 9999999.15-210&gt;9999999.18-1)</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:va-sct.display</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:va-sct.userSelected</t>
+  </si>
+  <si>
     <t>Observation.code.text</t>
   </si>
   <si>
@@ -1294,7 +1368,7 @@
     <t>Quantity.unit</t>
   </si>
   <si>
-    <t>1586-1: source value from V EXAM - UCUM CODE &gt; UCUM CODES - DESCRIPTION (9000010.13-221 &gt; 757.5-.01)</t>
+    <t>1586-1: source value from V EXAM - UCUM CODE &gt; UCUM CODES - DESCRIPTION OF THE UNIT (9000010.13-221 &gt; 757.5-.01)</t>
   </si>
   <si>
     <t>Dim.UCUMCode.DescriptionOfTheUnit</t>
@@ -2353,7 +2427,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR85"/>
+  <dimension ref="A1:AR94"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="78.4609375" customWidth="true" bestFit="true"/>
@@ -4700,7 +4774,7 @@
         <v>83</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>84</v>
@@ -4758,19 +4832,17 @@
         <v>84</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="AC19" s="2"/>
       <c r="AD19" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>84</v>
+        <v>231</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -4785,22 +4857,22 @@
         <v>107</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>240</v>
+        <v>84</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO19" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AM19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO19" t="s" s="2">
+      <c r="AP19" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>84</v>
@@ -4811,12 +4883,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="C20" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="B20" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>84</v>
       </c>
@@ -4828,25 +4902,29 @@
         <v>95</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>84</v>
       </c>
@@ -4894,25 +4972,25 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>84</v>
+        <v>245</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>84</v>
+        <v>246</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>84</v>
@@ -4921,10 +4999,10 @@
         <v>84</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>84</v>
+        <v>241</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>84</v>
@@ -4935,21 +5013,21 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>84</v>
@@ -4961,17 +5039,15 @@
         <v>84</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>141</v>
+        <v>222</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>142</v>
+        <v>223</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>84</v>
@@ -5008,31 +5084,31 @@
         <v>84</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>229</v>
+        <v>84</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>230</v>
+        <v>84</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>231</v>
+        <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>146</v>
+        <v>84</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>84</v>
@@ -5061,46 +5137,44 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>247</v>
+        <v>142</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>84</v>
       </c>
@@ -5109,7 +5183,7 @@
         <v>84</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>251</v>
+        <v>84</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>84</v>
@@ -5136,34 +5210,34 @@
         <v>84</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>84</v>
+        <v>229</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>84</v>
+        <v>231</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>253</v>
+        <v>84</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>84</v>
@@ -5175,10 +5249,10 @@
         <v>84</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>254</v>
+        <v>84</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>255</v>
+        <v>226</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>84</v>
@@ -5189,10 +5263,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5206,7 +5280,7 @@
         <v>95</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>84</v>
@@ -5215,18 +5289,20 @@
         <v>96</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>222</v>
+        <v>109</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>84</v>
       </c>
@@ -5235,7 +5311,7 @@
         <v>84</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>84</v>
+        <v>257</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>84</v>
@@ -5274,7 +5350,7 @@
         <v>84</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -5289,7 +5365,7 @@
         <v>107</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>84</v>
+        <v>259</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>84</v>
@@ -5301,10 +5377,10 @@
         <v>84</v>
       </c>
       <c r="AO23" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AP23" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="AQ23" t="s" s="2">
         <v>84</v>
@@ -5315,7 +5391,7 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>263</v>
@@ -5332,7 +5408,7 @@
         <v>95</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>84</v>
@@ -5341,7 +5417,7 @@
         <v>96</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>115</v>
+        <v>222</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>264</v>
@@ -5349,10 +5425,10 @@
       <c r="M24" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="N24" s="2"/>
-      <c r="O24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>266</v>
       </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>84</v>
       </c>
@@ -5415,22 +5491,22 @@
         <v>107</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="AL24" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>84</v>
@@ -5441,7 +5517,7 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>271</v>
@@ -5467,7 +5543,7 @@
         <v>96</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>222</v>
+        <v>115</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>272</v>
@@ -5544,7 +5620,7 @@
         <v>276</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>241</v>
+        <v>277</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>84</v>
@@ -5553,10 +5629,10 @@
         <v>84</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>84</v>
@@ -5567,10 +5643,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5584,7 +5660,7 @@
         <v>95</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>84</v>
@@ -5593,17 +5669,15 @@
         <v>96</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>280</v>
+        <v>222</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N26" t="s" s="2">
         <v>283</v>
       </c>
+      <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
         <v>284</v>
       </c>
@@ -5669,10 +5743,10 @@
         <v>107</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>84</v>
+        <v>286</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>84</v>
+        <v>246</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>84</v>
@@ -5681,10 +5755,10 @@
         <v>84</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>84</v>
@@ -5695,10 +5769,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5721,19 +5795,19 @@
         <v>96</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>222</v>
+        <v>291</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>84</v>
@@ -5782,7 +5856,7 @@
         <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5809,10 +5883,10 @@
         <v>84</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>84</v>
@@ -5823,12 +5897,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="D28" t="s" s="2">
         <v>84</v>
       </c>
@@ -5849,19 +5925,19 @@
         <v>96</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>297</v>
+        <v>234</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>298</v>
+        <v>235</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>299</v>
+        <v>236</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>300</v>
+        <v>237</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>301</v>
+        <v>238</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5910,13 +5986,13 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>296</v>
+        <v>240</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>84</v>
@@ -5925,25 +6001,25 @@
         <v>107</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>303</v>
+        <v>246</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>304</v>
+        <v>84</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>305</v>
+        <v>241</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>306</v>
+        <v>242</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>307</v>
+        <v>84</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>84</v>
@@ -5951,10 +6027,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>308</v>
+        <v>248</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5965,7 +6041,7 @@
         <v>82</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>84</v>
@@ -5974,20 +6050,18 @@
         <v>84</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>309</v>
+        <v>222</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>310</v>
+        <v>223</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -6036,19 +6110,19 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>308</v>
+        <v>225</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>84</v>
@@ -6063,13 +6137,13 @@
         <v>84</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>217</v>
+        <v>84</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>313</v>
+        <v>226</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>307</v>
+        <v>84</v>
       </c>
       <c r="AR29" t="s" s="2">
         <v>84</v>
@@ -6077,46 +6151,44 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>314</v>
+        <v>250</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>315</v>
+        <v>140</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>316</v>
+        <v>141</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>317</v>
+        <v>142</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>318</v>
+        <v>228</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>320</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>84</v>
       </c>
@@ -6152,52 +6224,52 @@
         <v>84</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>84</v>
+        <v>229</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>84</v>
+        <v>231</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>314</v>
+        <v>232</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>321</v>
+        <v>84</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>322</v>
+        <v>84</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>323</v>
+        <v>84</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>324</v>
+        <v>84</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>325</v>
+        <v>226</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>326</v>
+        <v>84</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>84</v>
@@ -6205,14 +6277,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>327</v>
+        <v>304</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>327</v>
+        <v>252</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>328</v>
+        <v>84</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -6222,7 +6294,7 @@
         <v>95</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>84</v>
@@ -6231,19 +6303,19 @@
         <v>96</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>329</v>
+        <v>109</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>330</v>
+        <v>253</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>331</v>
+        <v>254</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>332</v>
+        <v>255</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>333</v>
+        <v>256</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>84</v>
@@ -6253,7 +6325,7 @@
         <v>84</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>84</v>
+        <v>305</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>84</v>
@@ -6280,17 +6352,19 @@
         <v>84</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="AC31" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD31" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>231</v>
+        <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>327</v>
+        <v>258</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6305,25 +6379,25 @@
         <v>107</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>84</v>
+        <v>306</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>335</v>
+        <v>84</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>336</v>
+        <v>260</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>337</v>
+        <v>261</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>338</v>
+        <v>84</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>84</v>
@@ -6331,16 +6405,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>339</v>
+        <v>307</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>328</v>
+        <v>84</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -6350,7 +6422,7 @@
         <v>95</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>84</v>
@@ -6359,20 +6431,18 @@
         <v>96</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>341</v>
+        <v>222</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>330</v>
+        <v>264</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>331</v>
+        <v>265</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>333</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>84</v>
       </c>
@@ -6420,7 +6490,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>327</v>
+        <v>267</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6435,25 +6505,25 @@
         <v>107</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>342</v>
+        <v>84</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>343</v>
+        <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>335</v>
+        <v>84</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>336</v>
+        <v>268</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>337</v>
+        <v>269</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>338</v>
+        <v>84</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>84</v>
@@ -6461,10 +6531,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>344</v>
+        <v>308</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>344</v>
+        <v>271</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6478,7 +6548,7 @@
         <v>95</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>84</v>
@@ -6487,18 +6557,18 @@
         <v>96</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>345</v>
+        <v>115</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>346</v>
+        <v>272</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
       </c>
@@ -6546,7 +6616,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>344</v>
+        <v>275</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6561,10 +6631,10 @@
         <v>107</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>84</v>
+        <v>309</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>84</v>
+        <v>246</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>84</v>
@@ -6573,13 +6643,13 @@
         <v>84</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>349</v>
+        <v>278</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>350</v>
+        <v>279</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>351</v>
+        <v>84</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>84</v>
@@ -6587,10 +6657,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>352</v>
+        <v>310</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>352</v>
+        <v>281</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6601,10 +6671,10 @@
         <v>82</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>84</v>
@@ -6613,17 +6683,17 @@
         <v>96</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>353</v>
+        <v>222</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>354</v>
+        <v>282</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>355</v>
+        <v>283</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>356</v>
+        <v>284</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6672,13 +6742,13 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>352</v>
+        <v>285</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>84</v>
@@ -6687,25 +6757,25 @@
         <v>107</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>357</v>
+        <v>84</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>358</v>
+        <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>359</v>
+        <v>84</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>360</v>
+        <v>287</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>361</v>
+        <v>288</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>362</v>
+        <v>84</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>84</v>
@@ -6713,10 +6783,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>363</v>
+        <v>311</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>363</v>
+        <v>290</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6739,19 +6809,19 @@
         <v>96</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>364</v>
+        <v>291</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>365</v>
+        <v>292</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>366</v>
+        <v>293</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>367</v>
+        <v>294</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>368</v>
+        <v>295</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6788,17 +6858,19 @@
         <v>84</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="AC35" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>231</v>
+        <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>363</v>
+        <v>296</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6807,7 +6879,7 @@
         <v>95</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>369</v>
+        <v>84</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>107</v>
@@ -6822,31 +6894,29 @@
         <v>84</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>370</v>
+        <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>371</v>
+        <v>297</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>372</v>
+        <v>298</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>373</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>374</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>84</v>
       </c>
@@ -6858,7 +6928,7 @@
         <v>95</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>84</v>
@@ -6867,19 +6937,19 @@
         <v>96</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>376</v>
+        <v>222</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>365</v>
+        <v>313</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>366</v>
+        <v>314</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>367</v>
+        <v>315</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>368</v>
+        <v>316</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6928,7 +6998,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>363</v>
+        <v>317</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6937,13 +7007,13 @@
         <v>95</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>369</v>
+        <v>84</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>377</v>
+        <v>84</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>84</v>
@@ -6952,27 +7022,27 @@
         <v>84</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>370</v>
+        <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>371</v>
+        <v>318</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>373</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>378</v>
+        <v>320</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>379</v>
+        <v>320</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6986,25 +7056,29 @@
         <v>95</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>222</v>
+        <v>321</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>223</v>
+        <v>322</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>323</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
       </c>
@@ -7052,7 +7126,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>225</v>
+        <v>320</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -7064,28 +7138,28 @@
         <v>84</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>84</v>
+        <v>326</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>84</v>
+        <v>327</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>84</v>
+        <v>328</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>84</v>
+        <v>329</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>226</v>
+        <v>330</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>84</v>
+        <v>331</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>84</v>
@@ -7093,14 +7167,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>380</v>
+        <v>332</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>381</v>
+        <v>332</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -7116,19 +7190,19 @@
         <v>84</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>141</v>
+        <v>333</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>142</v>
+        <v>334</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>228</v>
+        <v>335</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>144</v>
+        <v>336</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7166,19 +7240,19 @@
         <v>84</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>229</v>
+        <v>84</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>230</v>
+        <v>84</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>231</v>
+        <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>232</v>
+        <v>332</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7190,7 +7264,7 @@
         <v>84</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>84</v>
@@ -7205,13 +7279,13 @@
         <v>84</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>84</v>
+        <v>217</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>226</v>
+        <v>337</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>84</v>
+        <v>331</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>84</v>
@@ -7219,14 +7293,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>382</v>
+        <v>338</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>383</v>
+        <v>338</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>84</v>
+        <v>339</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7245,19 +7319,19 @@
         <v>96</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>384</v>
+        <v>340</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>385</v>
+        <v>341</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>386</v>
+        <v>342</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>387</v>
+        <v>343</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>388</v>
+        <v>344</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7306,7 +7380,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>389</v>
+        <v>338</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7321,25 +7395,25 @@
         <v>107</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>390</v>
+        <v>345</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>84</v>
+        <v>346</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>84</v>
+        <v>347</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>391</v>
+        <v>348</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>392</v>
+        <v>349</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>84</v>
+        <v>350</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>84</v>
@@ -7347,14 +7421,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>393</v>
+        <v>351</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>394</v>
+        <v>351</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>84</v>
+        <v>352</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7367,30 +7441,30 @@
         <v>84</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="J40" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>115</v>
+        <v>353</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>395</v>
+        <v>354</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="O40" t="s" s="2">
-        <v>397</v>
+        <v>357</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q40" t="s" s="2">
-        <v>398</v>
-      </c>
+      <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
         <v>84</v>
       </c>
@@ -7410,31 +7484,29 @@
         <v>84</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>185</v>
+        <v>84</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>399</v>
+        <v>84</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>400</v>
+        <v>84</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>84</v>
+        <v>231</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>401</v>
+        <v>351</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7455,19 +7527,19 @@
         <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>84</v>
+        <v>359</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>402</v>
+        <v>360</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>403</v>
+        <v>361</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>84</v>
+        <v>362</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>84</v>
@@ -7475,14 +7547,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>404</v>
+        <v>363</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="C41" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="D41" t="s" s="2">
-        <v>84</v>
+        <v>352</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7501,17 +7575,19 @@
         <v>96</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>222</v>
+        <v>365</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>406</v>
+        <v>354</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="O41" t="s" s="2">
-        <v>408</v>
+        <v>357</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7560,7 +7636,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>409</v>
+        <v>351</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7575,25 +7651,25 @@
         <v>107</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>410</v>
+        <v>366</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>411</v>
+        <v>367</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>84</v>
+        <v>359</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>412</v>
+        <v>360</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>413</v>
+        <v>361</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>84</v>
+        <v>362</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>84</v>
@@ -7601,10 +7677,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>414</v>
+        <v>368</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>415</v>
+        <v>368</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7627,18 +7703,18 @@
         <v>96</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>109</v>
+        <v>369</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>416</v>
+        <v>370</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" t="s" s="2">
-        <v>418</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>84</v>
       </c>
@@ -7686,7 +7762,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>419</v>
+        <v>368</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7695,7 +7771,7 @@
         <v>95</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>420</v>
+        <v>84</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>107</v>
@@ -7713,13 +7789,13 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>412</v>
+        <v>373</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>421</v>
+        <v>374</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>84</v>
@@ -7727,10 +7803,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>422</v>
+        <v>376</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>423</v>
+        <v>376</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7741,7 +7817,7 @@
         <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>96</v>
@@ -7753,19 +7829,17 @@
         <v>96</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>115</v>
+        <v>377</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>424</v>
+        <v>378</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>426</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>427</v>
+        <v>380</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -7814,13 +7888,13 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>428</v>
+        <v>376</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>84</v>
@@ -7829,25 +7903,25 @@
         <v>107</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>429</v>
+        <v>381</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>430</v>
+        <v>382</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>84</v>
+        <v>383</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>412</v>
+        <v>384</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>431</v>
+        <v>385</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>84</v>
+        <v>386</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>84</v>
@@ -7855,10 +7929,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>432</v>
+        <v>387</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>432</v>
+        <v>387</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7878,22 +7952,22 @@
         <v>84</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>195</v>
+        <v>388</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>433</v>
+        <v>389</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>434</v>
+        <v>390</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>435</v>
+        <v>391</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>436</v>
+        <v>392</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -7918,31 +7992,29 @@
         <v>84</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>437</v>
+        <v>84</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>438</v>
+        <v>84</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>439</v>
+        <v>84</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>84</v>
+        <v>231</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>432</v>
+        <v>387</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7951,7 +8023,7 @@
         <v>95</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>440</v>
+        <v>393</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>107</v>
@@ -7966,38 +8038,40 @@
         <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>84</v>
+        <v>394</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>138</v>
+        <v>395</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>441</v>
+        <v>396</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>84</v>
+        <v>397</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>442</v>
+        <v>398</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="C45" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="D45" t="s" s="2">
-        <v>443</v>
+        <v>84</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>96</v>
@@ -8006,22 +8080,22 @@
         <v>84</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>195</v>
+        <v>400</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>444</v>
+        <v>389</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>445</v>
+        <v>390</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>446</v>
+        <v>391</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>447</v>
+        <v>392</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -8046,13 +8120,13 @@
         <v>84</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>437</v>
+        <v>84</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>448</v>
+        <v>84</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>449</v>
+        <v>84</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
@@ -8070,51 +8144,51 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>442</v>
+        <v>387</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>84</v>
+        <v>393</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>450</v>
+        <v>401</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>451</v>
+        <v>84</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>452</v>
+        <v>394</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>453</v>
+        <v>395</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>454</v>
+        <v>396</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>455</v>
+        <v>397</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>456</v>
+        <v>402</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>456</v>
+        <v>403</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8235,10 +8309,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>457</v>
+        <v>404</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>457</v>
+        <v>405</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8361,14 +8435,12 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>458</v>
+        <v>406</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>459</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>84</v>
       </c>
@@ -8380,27 +8452,29 @@
         <v>95</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>460</v>
+        <v>408</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>461</v>
+        <v>409</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>462</v>
+        <v>410</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>412</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
       </c>
@@ -8448,22 +8522,22 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>232</v>
+        <v>413</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>84</v>
+        <v>414</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>84</v>
@@ -8475,10 +8549,10 @@
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>138</v>
+        <v>415</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>138</v>
+        <v>416</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8489,10 +8563,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>464</v>
+        <v>417</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>465</v>
+        <v>418</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8509,26 +8583,30 @@
         <v>84</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>223</v>
+        <v>419</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>224</v>
+        <v>420</v>
       </c>
       <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q49" s="2"/>
+      <c r="Q49" t="s" s="2">
+        <v>422</v>
+      </c>
       <c r="R49" t="s" s="2">
         <v>84</v>
       </c>
@@ -8548,13 +8626,13 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>84</v>
+        <v>185</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>84</v>
+        <v>423</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>84</v>
+        <v>424</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8572,7 +8650,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>225</v>
+        <v>425</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8581,10 +8659,10 @@
         <v>95</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>466</v>
+        <v>84</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>84</v>
@@ -8599,10 +8677,10 @@
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>84</v>
+        <v>426</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>226</v>
+        <v>427</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8613,10 +8691,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>467</v>
+        <v>428</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>468</v>
+        <v>429</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8627,28 +8705,30 @@
         <v>82</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>141</v>
+        <v>222</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>469</v>
+        <v>430</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>470</v>
+        <v>431</v>
       </c>
       <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
       </c>
@@ -8684,37 +8764,37 @@
         <v>84</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>229</v>
+        <v>84</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>230</v>
+        <v>84</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>231</v>
+        <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>232</v>
+        <v>433</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>84</v>
+        <v>434</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>84</v>
+        <v>435</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>84</v>
@@ -8723,10 +8803,10 @@
         <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>84</v>
+        <v>436</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>84</v>
+        <v>437</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8737,10 +8817,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>471</v>
+        <v>438</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8748,7 +8828,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>95</v>
@@ -8760,27 +8840,27 @@
         <v>84</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K51" t="s" s="2">
         <v>109</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>473</v>
+        <v>440</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>441</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>442</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>476</v>
+        <v>84</v>
       </c>
       <c r="S51" t="s" s="2">
         <v>84</v>
@@ -8822,19 +8902,19 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>477</v>
+        <v>443</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>84</v>
+        <v>444</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>84</v>
@@ -8849,10 +8929,10 @@
         <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>84</v>
+        <v>436</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>138</v>
+        <v>445</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8863,10 +8943,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>478</v>
+        <v>446</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>479</v>
+        <v>447</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8874,31 +8954,35 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>480</v>
+        <v>115</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>481</v>
+        <v>448</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>449</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
       </c>
@@ -8907,7 +8991,7 @@
         <v>84</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>483</v>
+        <v>84</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>84</v>
@@ -8946,7 +9030,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>484</v>
+        <v>452</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8955,16 +9039,16 @@
         <v>95</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>485</v>
+        <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>84</v>
+        <v>453</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>84</v>
+        <v>454</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>84</v>
@@ -8973,10 +9057,10 @@
         <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>84</v>
+        <v>436</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>138</v>
+        <v>455</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8987,10 +9071,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>486</v>
+        <v>456</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>486</v>
+        <v>456</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9001,7 +9085,7 @@
         <v>82</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>84</v>
@@ -9010,22 +9094,22 @@
         <v>84</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>235</v>
+        <v>457</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>236</v>
+        <v>458</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>237</v>
+        <v>459</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>238</v>
+        <v>460</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -9050,13 +9134,13 @@
         <v>84</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>84</v>
+        <v>461</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>84</v>
+        <v>462</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>84</v>
+        <v>463</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>84</v>
@@ -9074,16 +9158,16 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>239</v>
+        <v>456</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>84</v>
+        <v>464</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>107</v>
@@ -9101,10 +9185,10 @@
         <v>84</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>242</v>
+        <v>138</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>243</v>
+        <v>465</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -9115,45 +9199,45 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>487</v>
+        <v>466</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>487</v>
+        <v>466</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>84</v>
+        <v>467</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>222</v>
+        <v>195</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>289</v>
+        <v>468</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>290</v>
+        <v>469</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>291</v>
+        <v>470</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>292</v>
+        <v>471</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -9178,13 +9262,13 @@
         <v>84</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>84</v>
+        <v>461</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>84</v>
+        <v>472</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>84</v>
+        <v>473</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>84</v>
@@ -9202,13 +9286,13 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>293</v>
+        <v>466</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>84</v>
@@ -9217,36 +9301,36 @@
         <v>107</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>84</v>
+        <v>474</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>84</v>
+        <v>475</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>84</v>
+        <v>476</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>294</v>
+        <v>477</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>295</v>
+        <v>478</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>84</v>
+        <v>479</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9257,7 +9341,7 @@
         <v>82</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>84</v>
@@ -9269,20 +9353,16 @@
         <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>489</v>
+        <v>222</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>490</v>
+        <v>223</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>493</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>84</v>
       </c>
@@ -9330,19 +9410,19 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>488</v>
+        <v>225</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>84</v>
@@ -9357,10 +9437,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>494</v>
+        <v>84</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>495</v>
+        <v>226</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9371,21 +9451,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>496</v>
+        <v>481</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>496</v>
+        <v>481</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>84</v>
@@ -9397,15 +9477,17 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>222</v>
+        <v>141</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>223</v>
+        <v>142</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>84</v>
@@ -9442,31 +9524,31 @@
         <v>84</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>84</v>
+        <v>229</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>84</v>
+        <v>231</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>84</v>
@@ -9495,21 +9577,23 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>497</v>
+        <v>482</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="C57" s="2"/>
+        <v>481</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="D57" t="s" s="2">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>84</v>
@@ -9521,16 +9605,16 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>141</v>
+        <v>484</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>142</v>
+        <v>485</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>228</v>
+        <v>486</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>144</v>
+        <v>487</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9568,16 +9652,16 @@
         <v>84</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>229</v>
+        <v>84</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>230</v>
+        <v>84</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>231</v>
+        <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>232</v>
@@ -9607,10 +9691,10 @@
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>226</v>
+        <v>138</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9621,10 +9705,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9644,20 +9728,18 @@
         <v>84</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>499</v>
+        <v>97</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>500</v>
+        <v>223</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>502</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9706,7 +9788,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>503</v>
+        <v>225</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9715,10 +9797,10 @@
         <v>95</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>84</v>
+        <v>490</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>84</v>
@@ -9733,10 +9815,10 @@
         <v>84</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>504</v>
+        <v>226</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9747,10 +9829,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>505</v>
+        <v>491</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9761,7 +9843,7 @@
         <v>82</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>84</v>
@@ -9770,16 +9852,16 @@
         <v>84</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>341</v>
+        <v>141</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>506</v>
+        <v>493</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9818,31 +9900,31 @@
         <v>84</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>84</v>
+        <v>229</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>84</v>
+        <v>231</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>508</v>
+        <v>232</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>84</v>
@@ -9857,10 +9939,10 @@
         <v>84</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>509</v>
+        <v>84</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9871,10 +9953,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>510</v>
+        <v>495</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>510</v>
+        <v>496</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9888,31 +9970,33 @@
         <v>95</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>511</v>
+        <v>109</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>512</v>
+        <v>497</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>498</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>499</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>84</v>
+        <v>500</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>84</v>
@@ -9954,7 +10038,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>95</v>
@@ -9966,13 +10050,13 @@
         <v>84</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>515</v>
+        <v>84</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>516</v>
+        <v>84</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>84</v>
@@ -9981,10 +10065,10 @@
         <v>84</v>
       </c>
       <c r="AO60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP60" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9995,10 +10079,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>518</v>
+        <v>502</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>518</v>
+        <v>503</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10006,7 +10090,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>95</v>
@@ -10021,17 +10105,15 @@
         <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>195</v>
+        <v>504</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>519</v>
+        <v>505</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>521</v>
-      </c>
+        <v>506</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -10041,7 +10123,7 @@
         <v>84</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>84</v>
+        <v>507</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>84</v>
@@ -10056,13 +10138,13 @@
         <v>84</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>212</v>
+        <v>84</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>522</v>
+        <v>84</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>523</v>
+        <v>84</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>84</v>
@@ -10080,7 +10162,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10089,7 +10171,7 @@
         <v>95</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>84</v>
+        <v>509</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>107</v>
@@ -10104,27 +10186,27 @@
         <v>84</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>524</v>
+        <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>525</v>
+        <v>84</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>526</v>
+        <v>138</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR61" t="s" s="2">
-        <v>527</v>
+        <v>84</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>528</v>
+        <v>510</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>528</v>
+        <v>510</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10135,7 +10217,7 @@
         <v>82</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>84</v>
@@ -10144,22 +10226,22 @@
         <v>84</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>195</v>
+        <v>234</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>529</v>
+        <v>235</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>530</v>
+        <v>236</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>531</v>
+        <v>237</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>532</v>
+        <v>238</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -10184,13 +10266,13 @@
         <v>84</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>212</v>
+        <v>84</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>533</v>
+        <v>84</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>534</v>
+        <v>84</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>84</v>
@@ -10208,13 +10290,13 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>528</v>
+        <v>240</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>84</v>
@@ -10235,10 +10317,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>535</v>
+        <v>241</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>536</v>
+        <v>242</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10249,10 +10331,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>537</v>
+        <v>511</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>537</v>
+        <v>511</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10272,21 +10354,23 @@
         <v>84</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>538</v>
+        <v>222</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>539</v>
+        <v>313</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>540</v>
+        <v>314</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>316</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
       </c>
@@ -10334,7 +10418,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>537</v>
+        <v>317</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10358,27 +10442,27 @@
         <v>84</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>542</v>
+        <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>543</v>
+        <v>318</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>544</v>
+        <v>319</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR63" t="s" s="2">
-        <v>545</v>
+        <v>84</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>546</v>
+        <v>512</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>546</v>
+        <v>512</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10389,7 +10473,7 @@
         <v>82</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>84</v>
@@ -10401,18 +10485,20 @@
         <v>84</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>547</v>
+        <v>513</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>548</v>
+        <v>514</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>549</v>
+        <v>515</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>516</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>517</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
       </c>
@@ -10460,13 +10546,13 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>546</v>
+        <v>512</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>84</v>
@@ -10484,27 +10570,27 @@
         <v>84</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>551</v>
+        <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>552</v>
+        <v>518</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>553</v>
+        <v>519</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR64" t="s" s="2">
-        <v>554</v>
+        <v>84</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>555</v>
+        <v>520</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>555</v>
+        <v>520</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10515,7 +10601,7 @@
         <v>82</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>84</v>
@@ -10527,20 +10613,16 @@
         <v>84</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>556</v>
+        <v>222</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>557</v>
+        <v>223</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>560</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>84</v>
       </c>
@@ -10588,19 +10670,19 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>555</v>
+        <v>225</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>561</v>
+        <v>84</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>84</v>
@@ -10615,10 +10697,10 @@
         <v>84</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>562</v>
+        <v>84</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>563</v>
+        <v>226</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -10629,21 +10711,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>564</v>
+        <v>521</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>564</v>
+        <v>521</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>84</v>
@@ -10655,15 +10737,17 @@
         <v>84</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>222</v>
+        <v>141</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>223</v>
+        <v>142</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>84</v>
@@ -10700,31 +10784,31 @@
         <v>84</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>84</v>
+        <v>229</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>84</v>
+        <v>231</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>84</v>
@@ -10753,21 +10837,21 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>565</v>
+        <v>522</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>565</v>
+        <v>522</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>84</v>
@@ -10776,19 +10860,19 @@
         <v>84</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>141</v>
+        <v>523</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>142</v>
+        <v>524</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>228</v>
+        <v>525</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>144</v>
+        <v>526</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10838,19 +10922,19 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>232</v>
+        <v>527</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>84</v>
@@ -10865,10 +10949,10 @@
         <v>84</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>226</v>
+        <v>528</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
@@ -10879,46 +10963,42 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>566</v>
+        <v>529</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>566</v>
+        <v>529</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>567</v>
+        <v>84</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="J68" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>141</v>
+        <v>365</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>568</v>
+        <v>530</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>531</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>84</v>
       </c>
@@ -10966,19 +11046,19 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>570</v>
+        <v>532</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>84</v>
@@ -10993,10 +11073,10 @@
         <v>84</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>138</v>
+        <v>533</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
@@ -11007,10 +11087,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>571</v>
+        <v>534</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>571</v>
+        <v>534</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11018,28 +11098,28 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>572</v>
+        <v>535</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>573</v>
+        <v>536</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>574</v>
+        <v>537</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11090,25 +11170,25 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>571</v>
+        <v>538</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>575</v>
+        <v>84</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>84</v>
+        <v>539</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>84</v>
+        <v>540</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>84</v>
@@ -11117,10 +11197,10 @@
         <v>84</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>576</v>
+        <v>138</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>577</v>
+        <v>541</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -11131,10 +11211,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>578</v>
+        <v>542</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>578</v>
+        <v>542</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11157,15 +11237,17 @@
         <v>84</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>572</v>
+        <v>195</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>579</v>
+        <v>543</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>544</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>545</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -11190,13 +11272,13 @@
         <v>84</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>84</v>
+        <v>212</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>84</v>
+        <v>546</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>84</v>
+        <v>547</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
@@ -11214,7 +11296,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>578</v>
+        <v>542</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11223,7 +11305,7 @@
         <v>95</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>575</v>
+        <v>84</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>107</v>
@@ -11238,27 +11320,27 @@
         <v>84</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>84</v>
+        <v>548</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>576</v>
+        <v>549</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>581</v>
+        <v>550</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>84</v>
+        <v>551</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>582</v>
+        <v>552</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>582</v>
+        <v>552</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11284,16 +11366,16 @@
         <v>195</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>583</v>
+        <v>553</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>584</v>
+        <v>554</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>585</v>
+        <v>555</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>586</v>
+        <v>556</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11318,13 +11400,13 @@
         <v>84</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>119</v>
+        <v>212</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>587</v>
+        <v>557</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>588</v>
+        <v>558</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11342,7 +11424,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>582</v>
+        <v>552</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11366,13 +11448,13 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>589</v>
+        <v>84</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>590</v>
+        <v>559</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>454</v>
+        <v>560</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
@@ -11383,10 +11465,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>591</v>
+        <v>561</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>591</v>
+        <v>561</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11397,7 +11479,7 @@
         <v>82</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>84</v>
@@ -11409,20 +11491,18 @@
         <v>84</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>195</v>
+        <v>562</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>592</v>
+        <v>563</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>593</v>
+        <v>564</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>595</v>
-      </c>
+        <v>565</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>84</v>
       </c>
@@ -11446,13 +11526,13 @@
         <v>84</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>212</v>
+        <v>84</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>596</v>
+        <v>84</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>597</v>
+        <v>84</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>84</v>
@@ -11470,13 +11550,13 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>591</v>
+        <v>561</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>84</v>
@@ -11494,27 +11574,27 @@
         <v>84</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>589</v>
+        <v>566</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>590</v>
+        <v>567</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>454</v>
+        <v>568</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR72" t="s" s="2">
-        <v>84</v>
+        <v>569</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>598</v>
+        <v>570</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>598</v>
+        <v>570</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11537,18 +11617,18 @@
         <v>84</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>599</v>
+        <v>571</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>600</v>
+        <v>572</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" t="s" s="2">
-        <v>602</v>
-      </c>
+        <v>573</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>84</v>
       </c>
@@ -11596,7 +11676,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>598</v>
+        <v>570</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11620,27 +11700,27 @@
         <v>84</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>84</v>
+        <v>575</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>84</v>
+        <v>576</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>603</v>
+        <v>577</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>84</v>
+        <v>578</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>604</v>
+        <v>579</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>604</v>
+        <v>579</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11651,7 +11731,7 @@
         <v>82</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>84</v>
@@ -11663,16 +11743,20 @@
         <v>84</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>222</v>
+        <v>580</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>605</v>
+        <v>581</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+        <v>582</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>584</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>84</v>
       </c>
@@ -11720,19 +11804,19 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>604</v>
+        <v>579</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>107</v>
+        <v>585</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>84</v>
@@ -11747,10 +11831,10 @@
         <v>84</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>576</v>
+        <v>586</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>607</v>
+        <v>587</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>84</v>
@@ -11761,10 +11845,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>608</v>
+        <v>588</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>608</v>
+        <v>588</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11775,7 +11859,7 @@
         <v>82</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>84</v>
@@ -11784,20 +11868,18 @@
         <v>84</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>609</v>
+        <v>222</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>610</v>
+        <v>223</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>612</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>84</v>
@@ -11846,19 +11928,19 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>608</v>
+        <v>225</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>84</v>
@@ -11873,10 +11955,10 @@
         <v>84</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>613</v>
+        <v>84</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>614</v>
+        <v>226</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
@@ -11887,14 +11969,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>615</v>
+        <v>589</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>615</v>
+        <v>589</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11910,19 +11992,19 @@
         <v>84</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>616</v>
+        <v>141</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>617</v>
+        <v>142</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>618</v>
+        <v>228</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>619</v>
+        <v>144</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11972,7 +12054,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>615</v>
+        <v>232</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -11984,7 +12066,7 @@
         <v>84</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>84</v>
@@ -11999,10 +12081,10 @@
         <v>84</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>613</v>
+        <v>84</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>620</v>
+        <v>226</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
@@ -12013,14 +12095,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>621</v>
+        <v>590</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>621</v>
+        <v>590</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>84</v>
+        <v>591</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -12033,25 +12115,25 @@
         <v>84</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="J77" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>556</v>
+        <v>141</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>622</v>
+        <v>592</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>623</v>
+        <v>593</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>624</v>
+        <v>144</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>625</v>
+        <v>150</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -12100,7 +12182,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>621</v>
+        <v>594</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12112,7 +12194,7 @@
         <v>84</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>84</v>
@@ -12127,10 +12209,10 @@
         <v>84</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>626</v>
+        <v>84</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>627</v>
+        <v>138</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
@@ -12141,10 +12223,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>628</v>
+        <v>595</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>628</v>
+        <v>595</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12167,13 +12249,13 @@
         <v>84</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>222</v>
+        <v>596</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>223</v>
+        <v>597</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>224</v>
+        <v>598</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -12224,7 +12306,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>225</v>
+        <v>595</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12233,10 +12315,10 @@
         <v>95</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>84</v>
+        <v>599</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>84</v>
@@ -12251,10 +12333,10 @@
         <v>84</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>84</v>
+        <v>600</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>226</v>
+        <v>601</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>84</v>
@@ -12265,21 +12347,21 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>629</v>
+        <v>602</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>629</v>
+        <v>602</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>84</v>
@@ -12291,17 +12373,15 @@
         <v>84</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>141</v>
+        <v>596</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>142</v>
+        <v>603</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>604</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>84</v>
@@ -12350,19 +12430,19 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>232</v>
+        <v>602</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>84</v>
+        <v>599</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>84</v>
@@ -12377,10 +12457,10 @@
         <v>84</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>84</v>
+        <v>600</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>226</v>
+        <v>605</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
@@ -12391,45 +12471,45 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>630</v>
+        <v>606</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>630</v>
+        <v>606</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>567</v>
+        <v>84</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>141</v>
+        <v>195</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>568</v>
+        <v>607</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>569</v>
+        <v>608</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>144</v>
+        <v>609</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>150</v>
+        <v>610</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>84</v>
@@ -12454,13 +12534,13 @@
         <v>84</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>84</v>
+        <v>611</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>84</v>
+        <v>612</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>84</v>
@@ -12478,19 +12558,19 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>570</v>
+        <v>606</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>84</v>
@@ -12502,13 +12582,13 @@
         <v>84</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>84</v>
+        <v>613</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>84</v>
+        <v>614</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>138</v>
+        <v>478</v>
       </c>
       <c r="AQ80" t="s" s="2">
         <v>84</v>
@@ -12519,10 +12599,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>631</v>
+        <v>615</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>631</v>
+        <v>615</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12530,10 +12610,10 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>84</v>
@@ -12542,22 +12622,22 @@
         <v>84</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K81" t="s" s="2">
         <v>195</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>632</v>
+        <v>616</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>633</v>
+        <v>617</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>634</v>
+        <v>618</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>211</v>
+        <v>619</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>84</v>
@@ -12585,10 +12665,10 @@
         <v>212</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>213</v>
+        <v>620</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>214</v>
+        <v>621</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>84</v>
@@ -12606,13 +12686,13 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>631</v>
+        <v>615</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>84</v>
@@ -12630,16 +12710,16 @@
         <v>84</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>635</v>
+        <v>613</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>217</v>
+        <v>614</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>218</v>
+        <v>478</v>
       </c>
       <c r="AQ81" t="s" s="2">
-        <v>219</v>
+        <v>84</v>
       </c>
       <c r="AR81" t="s" s="2">
         <v>84</v>
@@ -12647,10 +12727,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>636</v>
+        <v>622</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>636</v>
+        <v>622</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12670,22 +12750,20 @@
         <v>84</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>364</v>
+        <v>623</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>637</v>
+        <v>624</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>638</v>
-      </c>
+        <v>625</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>368</v>
+        <v>626</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>84</v>
@@ -12734,7 +12812,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>636</v>
+        <v>622</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12758,27 +12836,27 @@
         <v>84</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>639</v>
+        <v>84</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>371</v>
+        <v>84</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>372</v>
+        <v>627</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>373</v>
+        <v>84</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12801,20 +12879,16 @@
         <v>84</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>630</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>84</v>
       </c>
@@ -12838,13 +12912,13 @@
         <v>84</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>437</v>
+        <v>84</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>438</v>
+        <v>84</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>439</v>
+        <v>84</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>84</v>
@@ -12862,7 +12936,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -12871,7 +12945,7 @@
         <v>95</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>440</v>
+        <v>84</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>107</v>
@@ -12889,10 +12963,10 @@
         <v>84</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>138</v>
+        <v>600</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>441</v>
+        <v>631</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>84</v>
@@ -12903,14 +12977,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>443</v>
+        <v>84</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12926,23 +13000,21 @@
         <v>84</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>195</v>
+        <v>633</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>444</v>
+        <v>634</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>445</v>
+        <v>635</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>447</v>
-      </c>
+        <v>636</v>
+      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>84</v>
       </c>
@@ -12966,13 +13038,13 @@
         <v>84</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>437</v>
+        <v>84</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>448</v>
+        <v>84</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>449</v>
+        <v>84</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>84</v>
@@ -12990,7 +13062,7 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13014,27 +13086,27 @@
         <v>84</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>452</v>
+        <v>84</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>453</v>
+        <v>637</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>454</v>
+        <v>638</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR84" t="s" s="2">
-        <v>455</v>
+        <v>84</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13054,23 +13126,21 @@
         <v>84</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>85</v>
+        <v>640</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>560</v>
-      </c>
+        <v>643</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>84</v>
       </c>
@@ -13118,7 +13188,7 @@
         <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13145,20 +13215,1166 @@
         <v>84</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>562</v>
+        <v>637</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>563</v>
+        <v>644</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR85" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="P86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="AP86" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="AQ86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR86" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP87" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AQ87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR87" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP88" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AQ88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR88" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="P89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP89" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AQ89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR89" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="P90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AO90" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AP90" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AQ90" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AR90" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="P91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="AO91" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AP91" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AQ91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR91" t="s" s="2">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="P92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AP92" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AQ92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR92" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="P93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AP93" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AQ93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR93" t="s" s="2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="P94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AP94" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AQ94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR94" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR85">
+  <autoFilter ref="A1:AR94">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13168,7 +14384,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI84">
+  <conditionalFormatting sqref="A2:AI93">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1015,7 +1015,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Device|Location)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -1192,7 +1192,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1015,7 +1015,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
+    <t xml:space="preserve">Reference(Patient|Group|Device|Location)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2002,7 +2002,7 @@
     <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1015,7 +1015,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Device|Location)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -1075,7 +1075,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/EncounterOutpatient)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1594,7 +1594,7 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ConceptMap/CMVFExamResultInterpretation</t>
+    <t>http://va.gov/fhir/ConceptMap/ExamResultInterpretation</t>
   </si>
   <si>
     <t>Extension.value[x]</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -794,7 +794,7 @@
     <t>Outpat.VExam.ExamIEN</t>
   </si>
   <si>
-    <t>PhysicalExam.PhysExamCode,PhysicalExam.PhysExam.Description</t>
+    <t>PhysicalExam.PhysExamCode,PhysicalExam.PhysExamCode[PhysExam].Description</t>
   </si>
   <si>
     <t>Observation.code.coding:va-code.id</t>
@@ -1283,7 +1283,7 @@
     <t>1586: source value from V EXAM - UCUM CODE &gt; UCUM CODES (9000010.13-221 &gt; 757.5-)</t>
   </si>
   <si>
-    <t>PhysicalExam.PhysicalExamExtension.Units</t>
+    <t>PhysicalExam.Extension[PhysicalExamExtension].Units</t>
   </si>
   <si>
     <t>Observation.value[x]:valueQuantity.id</t>
@@ -1326,7 +1326,7 @@
     <t>1585: source value from V EXAM - MAGNITUDE (9000010.13-220)</t>
   </si>
   <si>
-    <t>PhysicalExam.PhysicalExamExtension.ResultValue</t>
+    <t>PhysicalExam.Extension[PhysicalExamExtension].ResultValue</t>
   </si>
   <si>
     <t>SN.2  / CQ - N/A</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file V EXAM (9000010.13) to Observation</t>
+    <t>This StructureDefinition contains the maps for VistA file V EXAM (9000010.13) to Observation.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -769,7 +769,7 @@
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:$this}
+    <t xml:space="preserve">value:$this}
 </t>
   </si>
   <si>
@@ -1615,7 +1615,7 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ConceptMap/ExamResultInterpretation</t>
+    <t>http://va.gov/fhir/ConceptMap/VF-ExamResultInterpretation</t>
   </si>
   <si>
     <t>Extension.value[x]</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -788,7 +788,7 @@
     <t>va-code</t>
   </si>
   <si>
-    <t>1580: source value from V EXAM - EXAM &gt; EXAM (9000010.13-.01 &gt; 9999999.15-)</t>
+    <t>1580: source value based on V EXAM - EXAM &gt; EXAM (9000010.13-.01 &gt; 9999999.15-)</t>
   </si>
   <si>
     <t>Outpat.VExam.ExamIEN</t>
@@ -884,7 +884,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1580-2: source value from V EXAM - EXAM &gt; EXAM - NAME (9000010.13-.01 &gt; 9999999.15-.01)</t>
+    <t>1580-2: source value based on V EXAM - EXAM &gt; EXAM - NAME (9000010.13-.01 &gt; 9999999.15-.01)</t>
   </si>
   <si>
     <t>Outpat.VExam.ExamIEN
@@ -915,7 +915,7 @@
     <t>Coding.display</t>
   </si>
   <si>
-    <t>1580-3: source value from V EXAM - EXAM &gt; EXAM - PRINT NAME (9000010.13-.01 &gt; 9999999.15-200)</t>
+    <t>1580-3: source value based on V EXAM - EXAM &gt; EXAM - PRINT NAME (9000010.13-.01 &gt; 9999999.15-200)</t>
   </si>
   <si>
     <t>C*E.2 - but note this is not well followed</t>
@@ -961,7 +961,7 @@
     <t>va-sct</t>
   </si>
   <si>
-    <t>1581: source value from V EXAM - EXAM &gt; EXAM - CODE MAPPINGS &gt; CODE MAPPINGS (9000010.13-.01 &gt; 9999999.15-210&gt;9999999.18)</t>
+    <t>1581: source value based on V EXAM - EXAM &gt; EXAM - CODE MAPPINGS &gt; CODE MAPPINGS (9000010.13-.01 &gt; 9999999.15-210&gt;9999999.18)</t>
   </si>
   <si>
     <t>Observation.code.coding:va-sct.id</t>
@@ -985,7 +985,7 @@
     <t>Observation.code.coding:va-sct.code</t>
   </si>
   <si>
-    <t>1581-2: source value from V EXAM - EXAM &gt; EXAM - CODE MAPPINGS &gt; CODE MAPPINGS - CODE (9000010.13-.01 &gt; 9999999.15-210&gt;9999999.18-1)</t>
+    <t>1581-2: source value based on V EXAM - EXAM &gt; EXAM - CODE MAPPINGS &gt; CODE MAPPINGS - CODE (9000010.13-.01 &gt; 9999999.15-210&gt;9999999.18-1)</t>
   </si>
   <si>
     <t>Observation.code.coding:va-sct.display</t>
@@ -1037,7 +1037,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>1582: reference from V EXAM - PATIENT NAME &gt; PATIENT/IHS - NAME (9000010.13-.02 &gt; 9000001-.01)</t>
+    <t>1582: reference based on V EXAM - PATIENT NAME &gt; PATIENT/IHS - NAME (9000010.13-.02 &gt; 9000001-.01)</t>
   </si>
   <si>
     <t>Outpat.VExam.PatientIEN</t>
@@ -1097,7 +1097,7 @@
     <t>For some observations it may be important to know the link between an observation and a particular encounter.</t>
   </si>
   <si>
-    <t>1583: reference from V EXAM - VISIT (9000010.13-.03)</t>
+    <t>1583: reference based on V EXAM - VISIT (9000010.13-.03)</t>
   </si>
   <si>
     <t>Outpat.VExam.VisitDateTime,Outpat.VExam.VisitIEN</t>
@@ -1167,7 +1167,7 @@
 </t>
   </si>
   <si>
-    <t>1588: source value from V EXAM - EVENT DATE AND TIME (9000010.13-1201)</t>
+    <t>1588: source value based on V EXAM - EVENT DATE AND TIME (9000010.13-1201)</t>
   </si>
   <si>
     <t>Outpat.VExam.EventDateTime</t>
@@ -1217,7 +1217,7 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
-    <t>1590: reference from V EXAM - ENCOUNTER PROVIDER (9000010.13-1204)</t>
+    <t>1590: reference based on V EXAM - ENCOUNTER PROVIDER (9000010.13-1204)</t>
   </si>
   <si>
     <t>Outpat.VExam.EncounterProviderIEN</t>
@@ -1280,7 +1280,7 @@
 </t>
   </si>
   <si>
-    <t>1586: source value from V EXAM - UCUM CODE &gt; UCUM CODES (9000010.13-221 &gt; 757.5-)</t>
+    <t>1586: source value based on V EXAM - UCUM CODE &gt; UCUM CODES (9000010.13-221 &gt; 757.5-)</t>
   </si>
   <si>
     <t>PhysicalExam.Extension[PhysicalExamExtension].Units</t>
@@ -1323,7 +1323,7 @@
     <t>Quantity.value</t>
   </si>
   <si>
-    <t>1585: source value from V EXAM - MAGNITUDE (9000010.13-220)</t>
+    <t>1585: source value based on V EXAM - MAGNITUDE (9000010.13-220)</t>
   </si>
   <si>
     <t>PhysicalExam.Extension[PhysicalExamExtension].ResultValue</t>
@@ -1386,7 +1386,7 @@
     <t>Quantity.unit</t>
   </si>
   <si>
-    <t>1586-1: source value from V EXAM - UCUM CODE &gt; UCUM CODES - DESCRIPTION OF THE UNIT (9000010.13-221 &gt; 757.5-.01)</t>
+    <t>1586-1: source value based on V EXAM - UCUM CODE &gt; UCUM CODES - DESCRIPTION OF THE UNIT (9000010.13-221 &gt; 757.5-.01)</t>
   </si>
   <si>
     <t>Dim.UCUMCode.DescriptionOfTheUnit</t>
@@ -1444,7 +1444,7 @@
     <t>Quantity.code</t>
   </si>
   <si>
-    <t>1586-2: source value from V EXAM - UCUM CODE &gt; UCUM CODES - UCUM CODE (9000010.13-221 &gt; 757.5-1)</t>
+    <t>1586-2: source value based on V EXAM - UCUM CODE &gt; UCUM CODES - UCUM CODE (9000010.13-221 &gt; 757.5-1)</t>
   </si>
   <si>
     <t>Dim.UCUMCode.UCUMCode</t>
@@ -1715,7 +1715,7 @@
     <t>Annotation.text</t>
   </si>
   <si>
-    <t>1587: source value from V EXAM - COMMENTS (9000010.13-81101)</t>
+    <t>1587: source value based on V EXAM - COMMENTS (9000010.13-81101)</t>
   </si>
   <si>
     <t>Outpat.VExam.Comments</t>
@@ -2489,7 +2489,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="139.59375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="143.6875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="49.3203125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="100.86328125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$85</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3918" uniqueCount="680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3550" uniqueCount="649">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1498,7 +1498,7 @@
     <t>A categorical assessment of an observation value.  For example, high, low, normal.</t>
   </si>
   <si>
-    <t>Historically used for laboratory results (known as 'abnormal flag' ),  its use extends to other use cases where coded interpretations  are relevant.  Often reported as one or more simple compact codes this element is often placed adjacent to the result value in reports and flow sheets to signal the meaning/normalcy status of the result.</t>
+    <t>see mapping [VF_ExamResultInterpretation](ConceptMap-VF-ExamResultInterpretation.html)</t>
   </si>
   <si>
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
@@ -1529,106 +1529,6 @@
   </si>
   <si>
     <t>363713009 |Has interpretation|</t>
-  </si>
-  <si>
-    <t>Observation.interpretation.id</t>
-  </si>
-  <si>
-    <t>Observation.interpretation.extension</t>
-  </si>
-  <si>
-    <t>Observation.interpretation.extension:11179-permitted-value-conceptmap</t>
-  </si>
-  <si>
-    <t>11179-permitted-value-conceptmap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {11179-permitted-value-conceptmap}
-</t>
-  </si>
-  <si>
-    <t>Mapping from permitted to transmitted</t>
-  </si>
-  <si>
-    <t>Expresses the linkage between the internal codes used for storage and the codes used for exchange.</t>
-  </si>
-  <si>
-    <t>The permitted value set must have a 1..1 set of codes for each code in the value meaning value set.  The source for the concept map is the value set the extension appears on.  The target is the permitted-value-valueset.</t>
-  </si>
-  <si>
-    <t>Observation.interpretation.extension:11179-permitted-value-conceptmap.id</t>
-  </si>
-  <si>
-    <t>Observation.interpretation.extension.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>Observation.interpretation.extension:11179-permitted-value-conceptmap.extension</t>
-  </si>
-  <si>
-    <t>Observation.interpretation.extension.extension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>Observation.interpretation.extension:11179-permitted-value-conceptmap.url</t>
-  </si>
-  <si>
-    <t>Observation.interpretation.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/11179-permitted-value-conceptmap</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>Observation.interpretation.extension:11179-permitted-value-conceptmap.value[x]</t>
-  </si>
-  <si>
-    <t>Observation.interpretation.extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(ConceptMap)
-</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ConceptMap/VF-ExamResultInterpretation</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ext-1
-</t>
-  </si>
-  <si>
-    <t>Observation.interpretation.coding</t>
-  </si>
-  <si>
-    <t>Observation.interpretation.text</t>
   </si>
   <si>
     <t>Observation.note</t>
@@ -2126,6 +2026,9 @@
   </si>
   <si>
     <t>Observation.component.interpretation</t>
+  </si>
+  <si>
+    <t>Historically used for laboratory results (known as 'abnormal flag' ),  its use extends to other use cases where coded interpretations  are relevant.  Often reported as one or more simple compact codes this element is often placed adjacent to the result value in reports and flow sheets to signal the meaning/normalcy status of the result.</t>
   </si>
   <si>
     <t>Observation.component.referenceRange</t>
@@ -2451,12 +2354,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS94"/>
+  <dimension ref="A1:AS85"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="78.4609375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.1171875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="34.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="17.96484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -9528,7 +9431,7 @@
         <v>83</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>85</v>
@@ -9540,16 +9443,20 @@
         <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>223</v>
+        <v>488</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>224</v>
+        <v>489</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+        <v>490</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>492</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>85</v>
       </c>
@@ -9597,19 +9504,19 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>226</v>
+        <v>487</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>85</v>
@@ -9627,10 +9534,10 @@
         <v>85</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>85</v>
+        <v>493</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>227</v>
+        <v>494</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>85</v>
@@ -9641,21 +9548,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>141</v>
+        <v>85</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>85</v>
@@ -9667,17 +9574,15 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>142</v>
+        <v>223</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>143</v>
+        <v>224</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>85</v>
@@ -9714,31 +9619,31 @@
         <v>85</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>230</v>
+        <v>85</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>231</v>
+        <v>85</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>232</v>
+        <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>147</v>
+        <v>85</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>85</v>
@@ -9770,23 +9675,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>490</v>
-      </c>
+        <v>496</v>
+      </c>
+      <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>85</v>
@@ -9798,16 +9701,16 @@
         <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>491</v>
+        <v>142</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>492</v>
+        <v>143</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>493</v>
+        <v>229</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>494</v>
+        <v>145</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9845,16 +9748,16 @@
         <v>85</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>85</v>
+        <v>230</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>85</v>
+        <v>231</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>85</v>
+        <v>232</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>233</v>
@@ -9887,10 +9790,10 @@
         <v>85</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>139</v>
+        <v>227</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9901,10 +9804,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9924,18 +9827,20 @@
         <v>85</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>98</v>
+        <v>498</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>224</v>
+        <v>499</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>500</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>501</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>85</v>
@@ -9984,7 +9889,7 @@
         <v>85</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>226</v>
+        <v>502</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -9993,10 +9898,10 @@
         <v>96</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>497</v>
+        <v>85</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>85</v>
@@ -10014,10 +9919,10 @@
         <v>85</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>227</v>
+        <v>503</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>85</v>
@@ -10028,10 +9933,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10042,7 +9947,7 @@
         <v>83</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>85</v>
@@ -10051,16 +9956,16 @@
         <v>85</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>142</v>
+        <v>368</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -10099,31 +10004,31 @@
         <v>85</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>230</v>
+        <v>85</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>231</v>
+        <v>85</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>232</v>
+        <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>233</v>
+        <v>507</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>85</v>
@@ -10141,10 +10046,10 @@
         <v>85</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>85</v>
+        <v>508</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>85</v>
@@ -10155,10 +10060,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10172,33 +10077,31 @@
         <v>96</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>110</v>
+        <v>510</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>506</v>
-      </c>
+        <v>512</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>507</v>
+        <v>85</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>85</v>
@@ -10240,7 +10143,7 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>96</v>
@@ -10252,16 +10155,16 @@
         <v>85</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>85</v>
+        <v>514</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>85</v>
+        <v>515</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>85</v>
+        <v>516</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>85</v>
@@ -10270,10 +10173,10 @@
         <v>85</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>139</v>
+        <v>517</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>85</v>
@@ -10284,10 +10187,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10295,7 +10198,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>96</v>
@@ -10310,15 +10213,17 @@
         <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>511</v>
+        <v>196</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>520</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>521</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>85</v>
@@ -10328,7 +10233,7 @@
         <v>85</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>514</v>
+        <v>85</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>85</v>
@@ -10343,13 +10248,13 @@
         <v>85</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>85</v>
+        <v>213</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>85</v>
+        <v>522</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>85</v>
+        <v>523</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>85</v>
@@ -10367,7 +10272,7 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -10376,7 +10281,7 @@
         <v>96</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>516</v>
+        <v>85</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>108</v>
@@ -10394,27 +10299,27 @@
         <v>85</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>85</v>
+        <v>524</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>85</v>
+        <v>525</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>139</v>
+        <v>526</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS61" t="s" s="2">
-        <v>85</v>
+        <v>527</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10425,7 +10330,7 @@
         <v>83</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>85</v>
@@ -10434,22 +10339,22 @@
         <v>85</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>235</v>
+        <v>196</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>236</v>
+        <v>529</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>237</v>
+        <v>530</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>238</v>
+        <v>531</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>239</v>
+        <v>532</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>85</v>
@@ -10474,13 +10379,13 @@
         <v>85</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>85</v>
+        <v>213</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>85</v>
+        <v>533</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>85</v>
+        <v>534</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>85</v>
@@ -10498,13 +10403,13 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>241</v>
+        <v>528</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>85</v>
@@ -10528,10 +10433,10 @@
         <v>85</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>242</v>
+        <v>535</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>243</v>
+        <v>536</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -10542,10 +10447,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>518</v>
+        <v>537</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>518</v>
+        <v>537</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10565,23 +10470,21 @@
         <v>85</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>223</v>
+        <v>538</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>315</v>
+        <v>539</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>316</v>
+        <v>540</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>541</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>85</v>
       </c>
@@ -10629,7 +10532,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>319</v>
+        <v>537</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10656,27 +10559,27 @@
         <v>85</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>85</v>
+        <v>542</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>320</v>
+        <v>543</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>321</v>
+        <v>544</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS63" t="s" s="2">
-        <v>85</v>
+        <v>545</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>519</v>
+        <v>546</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>519</v>
+        <v>546</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10687,7 +10590,7 @@
         <v>83</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>85</v>
@@ -10699,20 +10602,18 @@
         <v>85</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>520</v>
+        <v>547</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>521</v>
+        <v>548</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>522</v>
+        <v>549</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>524</v>
-      </c>
+        <v>550</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>85</v>
       </c>
@@ -10760,13 +10661,13 @@
         <v>85</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>519</v>
+        <v>546</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>85</v>
@@ -10787,27 +10688,27 @@
         <v>85</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>85</v>
+        <v>551</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>525</v>
+        <v>552</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>526</v>
+        <v>553</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS64" t="s" s="2">
-        <v>85</v>
+        <v>554</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>527</v>
+        <v>555</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>527</v>
+        <v>555</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10818,7 +10719,7 @@
         <v>83</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>85</v>
@@ -10830,16 +10731,20 @@
         <v>85</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>223</v>
+        <v>556</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>224</v>
+        <v>557</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+        <v>558</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>560</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>85</v>
       </c>
@@ -10887,19 +10792,19 @@
         <v>85</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>226</v>
+        <v>555</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>85</v>
+        <v>561</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>85</v>
@@ -10917,10 +10822,10 @@
         <v>85</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>85</v>
+        <v>562</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>227</v>
+        <v>563</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>85</v>
@@ -10931,21 +10836,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>528</v>
+        <v>564</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>528</v>
+        <v>564</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>141</v>
+        <v>85</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>85</v>
@@ -10957,17 +10862,15 @@
         <v>85</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>142</v>
+        <v>223</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>143</v>
+        <v>224</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>85</v>
@@ -11004,31 +10907,31 @@
         <v>85</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>230</v>
+        <v>85</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>231</v>
+        <v>85</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>232</v>
+        <v>85</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>147</v>
+        <v>85</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>85</v>
@@ -11060,21 +10963,21 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>529</v>
+        <v>565</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>529</v>
+        <v>565</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>85</v>
@@ -11083,19 +10986,19 @@
         <v>85</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>530</v>
+        <v>142</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>531</v>
+        <v>143</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>532</v>
+        <v>229</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>533</v>
+        <v>145</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -11145,19 +11048,19 @@
         <v>85</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>534</v>
+        <v>233</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>85</v>
@@ -11175,10 +11078,10 @@
         <v>85</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>535</v>
+        <v>227</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>85</v>
@@ -11189,42 +11092,46 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>536</v>
+        <v>566</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>536</v>
+        <v>566</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>85</v>
+        <v>567</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="J68" t="s" s="2">
         <v>97</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>368</v>
+        <v>142</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>537</v>
+        <v>568</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>569</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>85</v>
       </c>
@@ -11272,19 +11179,19 @@
         <v>85</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>539</v>
+        <v>570</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>85</v>
@@ -11302,10 +11209,10 @@
         <v>85</v>
       </c>
       <c r="AP68" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ68" t="s" s="2">
         <v>139</v>
-      </c>
-      <c r="AQ68" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>85</v>
@@ -11316,10 +11223,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>541</v>
+        <v>571</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>541</v>
+        <v>571</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11327,28 +11234,28 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>96</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>542</v>
+        <v>572</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>543</v>
+        <v>573</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>544</v>
+        <v>574</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11399,28 +11306,28 @@
         <v>85</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>545</v>
+        <v>571</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>85</v>
+        <v>575</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>108</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>546</v>
+        <v>85</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>547</v>
+        <v>85</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>548</v>
+        <v>85</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>85</v>
@@ -11429,10 +11336,10 @@
         <v>85</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>139</v>
+        <v>576</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>549</v>
+        <v>577</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>85</v>
@@ -11443,10 +11350,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>550</v>
+        <v>578</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>550</v>
+        <v>578</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11469,17 +11376,15 @@
         <v>85</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>196</v>
+        <v>572</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>551</v>
+        <v>579</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>553</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>85</v>
@@ -11504,13 +11409,13 @@
         <v>85</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>213</v>
+        <v>85</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>554</v>
+        <v>85</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>555</v>
+        <v>85</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>85</v>
@@ -11528,7 +11433,7 @@
         <v>85</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>550</v>
+        <v>578</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
@@ -11537,7 +11442,7 @@
         <v>96</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>85</v>
+        <v>575</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>108</v>
@@ -11555,27 +11460,27 @@
         <v>85</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>556</v>
+        <v>85</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>557</v>
+        <v>576</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>558</v>
+        <v>581</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS70" t="s" s="2">
-        <v>559</v>
+        <v>85</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>560</v>
+        <v>582</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>560</v>
+        <v>582</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11601,16 +11506,16 @@
         <v>196</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>561</v>
+        <v>583</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>562</v>
+        <v>584</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>563</v>
+        <v>585</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>564</v>
+        <v>586</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>85</v>
@@ -11635,13 +11540,13 @@
         <v>85</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>213</v>
+        <v>120</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>565</v>
+        <v>587</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>566</v>
+        <v>588</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>85</v>
@@ -11659,7 +11564,7 @@
         <v>85</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>560</v>
+        <v>582</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
@@ -11686,13 +11591,13 @@
         <v>85</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>85</v>
+        <v>589</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>568</v>
+        <v>485</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>85</v>
@@ -11703,10 +11608,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>569</v>
+        <v>591</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>569</v>
+        <v>591</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11717,7 +11622,7 @@
         <v>83</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>85</v>
@@ -11729,18 +11634,20 @@
         <v>85</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>570</v>
+        <v>196</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>571</v>
+        <v>592</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>572</v>
+        <v>593</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="O72" s="2"/>
+        <v>594</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>595</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>85</v>
       </c>
@@ -11764,13 +11671,13 @@
         <v>85</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>85</v>
+        <v>213</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>85</v>
+        <v>596</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>85</v>
+        <v>597</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>85</v>
@@ -11788,13 +11695,13 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>569</v>
+        <v>591</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>85</v>
@@ -11815,27 +11722,27 @@
         <v>85</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>574</v>
+        <v>589</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>575</v>
+        <v>590</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>576</v>
+        <v>485</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS72" t="s" s="2">
-        <v>577</v>
+        <v>85</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>578</v>
+        <v>598</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>578</v>
+        <v>598</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11858,18 +11765,18 @@
         <v>85</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>579</v>
+        <v>599</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>601</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" t="s" s="2">
+        <v>602</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>85</v>
       </c>
@@ -11917,7 +11824,7 @@
         <v>85</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>578</v>
+        <v>598</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>83</v>
@@ -11944,27 +11851,27 @@
         <v>85</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>583</v>
+        <v>85</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>584</v>
+        <v>85</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>585</v>
+        <v>603</v>
       </c>
       <c r="AR73" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS73" t="s" s="2">
-        <v>586</v>
+        <v>85</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>587</v>
+        <v>604</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>587</v>
+        <v>604</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11975,7 +11882,7 @@
         <v>83</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>85</v>
@@ -11987,20 +11894,16 @@
         <v>85</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>588</v>
+        <v>223</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>589</v>
+        <v>605</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>592</v>
-      </c>
+        <v>606</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>85</v>
       </c>
@@ -12048,19 +11951,19 @@
         <v>85</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>587</v>
+        <v>604</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>593</v>
+        <v>108</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>85</v>
@@ -12078,10 +11981,10 @@
         <v>85</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>594</v>
+        <v>576</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>595</v>
+        <v>607</v>
       </c>
       <c r="AR74" t="s" s="2">
         <v>85</v>
@@ -12092,10 +11995,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>596</v>
+        <v>608</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>596</v>
+        <v>608</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12106,7 +12009,7 @@
         <v>83</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>85</v>
@@ -12115,18 +12018,20 @@
         <v>85</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>223</v>
+        <v>609</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>224</v>
+        <v>610</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>611</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>612</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>85</v>
@@ -12175,19 +12080,19 @@
         <v>85</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>226</v>
+        <v>608</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>85</v>
@@ -12205,10 +12110,10 @@
         <v>85</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>85</v>
+        <v>613</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>227</v>
+        <v>614</v>
       </c>
       <c r="AR75" t="s" s="2">
         <v>85</v>
@@ -12219,14 +12124,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>597</v>
+        <v>615</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>597</v>
+        <v>615</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>141</v>
+        <v>85</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -12242,19 +12147,19 @@
         <v>85</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>142</v>
+        <v>616</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>143</v>
+        <v>617</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>229</v>
+        <v>618</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>145</v>
+        <v>619</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -12304,7 +12209,7 @@
         <v>85</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>233</v>
+        <v>615</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>83</v>
@@ -12316,7 +12221,7 @@
         <v>85</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>85</v>
@@ -12334,10 +12239,10 @@
         <v>85</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>85</v>
+        <v>613</v>
       </c>
       <c r="AQ76" t="s" s="2">
-        <v>227</v>
+        <v>620</v>
       </c>
       <c r="AR76" t="s" s="2">
         <v>85</v>
@@ -12348,14 +12253,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>598</v>
+        <v>621</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>598</v>
+        <v>621</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>599</v>
+        <v>85</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -12368,25 +12273,25 @@
         <v>85</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="J77" t="s" s="2">
         <v>97</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>142</v>
+        <v>556</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>600</v>
+        <v>622</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>601</v>
+        <v>623</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>145</v>
+        <v>624</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>151</v>
+        <v>625</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>85</v>
@@ -12435,7 +12340,7 @@
         <v>85</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>602</v>
+        <v>621</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>83</v>
@@ -12447,7 +12352,7 @@
         <v>85</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>85</v>
@@ -12465,10 +12370,10 @@
         <v>85</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>85</v>
+        <v>626</v>
       </c>
       <c r="AQ77" t="s" s="2">
-        <v>139</v>
+        <v>627</v>
       </c>
       <c r="AR77" t="s" s="2">
         <v>85</v>
@@ -12479,10 +12384,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>603</v>
+        <v>628</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>603</v>
+        <v>628</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12505,13 +12410,13 @@
         <v>85</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>604</v>
+        <v>223</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>605</v>
+        <v>224</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>606</v>
+        <v>225</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -12562,7 +12467,7 @@
         <v>85</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>603</v>
+        <v>226</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>83</v>
@@ -12571,10 +12476,10 @@
         <v>96</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>607</v>
+        <v>85</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>85</v>
@@ -12592,10 +12497,10 @@
         <v>85</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>608</v>
+        <v>85</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>609</v>
+        <v>227</v>
       </c>
       <c r="AR78" t="s" s="2">
         <v>85</v>
@@ -12606,21 +12511,21 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>610</v>
+        <v>629</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>610</v>
+        <v>629</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>85</v>
@@ -12632,15 +12537,17 @@
         <v>85</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>604</v>
+        <v>142</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>611</v>
+        <v>143</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="N79" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>85</v>
@@ -12689,19 +12596,19 @@
         <v>85</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>610</v>
+        <v>233</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>607</v>
+        <v>85</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>85</v>
@@ -12719,10 +12626,10 @@
         <v>85</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>608</v>
+        <v>85</v>
       </c>
       <c r="AQ79" t="s" s="2">
-        <v>613</v>
+        <v>227</v>
       </c>
       <c r="AR79" t="s" s="2">
         <v>85</v>
@@ -12733,45 +12640,45 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>614</v>
+        <v>630</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>614</v>
+        <v>630</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>85</v>
+        <v>567</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>196</v>
+        <v>142</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>615</v>
+        <v>568</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>616</v>
+        <v>569</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>617</v>
+        <v>145</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>618</v>
+        <v>151</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>85</v>
@@ -12796,13 +12703,13 @@
         <v>85</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>619</v>
+        <v>85</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>620</v>
+        <v>85</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>85</v>
@@ -12820,19 +12727,19 @@
         <v>85</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>614</v>
+        <v>570</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>85</v>
@@ -12847,13 +12754,13 @@
         <v>85</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>621</v>
+        <v>85</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>622</v>
+        <v>85</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>485</v>
+        <v>139</v>
       </c>
       <c r="AR80" t="s" s="2">
         <v>85</v>
@@ -12864,10 +12771,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12875,10 +12782,10 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>85</v>
@@ -12887,22 +12794,22 @@
         <v>85</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K81" t="s" s="2">
         <v>196</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>627</v>
+        <v>212</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>85</v>
@@ -12930,10 +12837,10 @@
         <v>213</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>628</v>
+        <v>214</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>629</v>
+        <v>215</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>85</v>
@@ -12951,13 +12858,13 @@
         <v>85</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>85</v>
@@ -12978,16 +12885,16 @@
         <v>85</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>621</v>
+        <v>635</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>622</v>
+        <v>218</v>
       </c>
       <c r="AQ81" t="s" s="2">
-        <v>485</v>
+        <v>219</v>
       </c>
       <c r="AR81" t="s" s="2">
-        <v>85</v>
+        <v>220</v>
       </c>
       <c r="AS81" t="s" s="2">
         <v>85</v>
@@ -12995,10 +12902,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13018,20 +12925,22 @@
         <v>85</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>631</v>
+        <v>392</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>638</v>
+      </c>
       <c r="O82" t="s" s="2">
-        <v>634</v>
+        <v>396</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>85</v>
@@ -13080,7 +12989,7 @@
         <v>85</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>83</v>
@@ -13107,27 +13016,27 @@
         <v>85</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>85</v>
+        <v>639</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>85</v>
+        <v>399</v>
       </c>
       <c r="AQ82" t="s" s="2">
-        <v>635</v>
+        <v>400</v>
       </c>
       <c r="AR82" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS82" t="s" s="2">
-        <v>85</v>
+        <v>401</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13150,16 +13059,20 @@
         <v>85</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
+        <v>642</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>85</v>
       </c>
@@ -13183,13 +13096,13 @@
         <v>85</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>85</v>
+        <v>467</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>85</v>
+        <v>468</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>85</v>
+        <v>469</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>85</v>
@@ -13207,7 +13120,7 @@
         <v>85</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>83</v>
@@ -13216,7 +13129,7 @@
         <v>96</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>85</v>
+        <v>470</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>108</v>
@@ -13237,10 +13150,10 @@
         <v>85</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>608</v>
+        <v>139</v>
       </c>
       <c r="AQ83" t="s" s="2">
-        <v>639</v>
+        <v>471</v>
       </c>
       <c r="AR83" t="s" s="2">
         <v>85</v>
@@ -13251,14 +13164,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>85</v>
+        <v>473</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -13274,21 +13187,23 @@
         <v>85</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>641</v>
+        <v>196</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>642</v>
+        <v>474</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>643</v>
+        <v>475</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="O84" s="2"/>
+        <v>645</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>85</v>
       </c>
@@ -13312,13 +13227,13 @@
         <v>85</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>85</v>
+        <v>467</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>85</v>
+        <v>478</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>85</v>
+        <v>479</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>85</v>
@@ -13336,7 +13251,7 @@
         <v>85</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>83</v>
@@ -13363,27 +13278,27 @@
         <v>85</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>85</v>
+        <v>483</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>645</v>
+        <v>484</v>
       </c>
       <c r="AQ84" t="s" s="2">
-        <v>646</v>
+        <v>485</v>
       </c>
       <c r="AR84" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS84" t="s" s="2">
-        <v>85</v>
+        <v>486</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13403,21 +13318,23 @@
         <v>85</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="L85" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>650</v>
-      </c>
       <c r="N85" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="O85" s="2"/>
+        <v>559</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>560</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>85</v>
       </c>
@@ -13465,7 +13382,7 @@
         <v>85</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>83</v>
@@ -13495,1193 +13412,20 @@
         <v>85</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>645</v>
+        <v>562</v>
       </c>
       <c r="AQ85" t="s" s="2">
-        <v>652</v>
+        <v>563</v>
       </c>
       <c r="AR85" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS85" t="s" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="86" hidden="true">
-      <c r="A86" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="C86" s="2"/>
-      <c r="D86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E86" s="2"/>
-      <c r="F86" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G86" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J86" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="K86" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="L86" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="P86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q86" s="2"/>
-      <c r="R86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="AG86" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH86" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ86" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AK86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP86" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="AQ86" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="AR86" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS86" t="s" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="87" hidden="true">
-      <c r="A87" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="C87" s="2"/>
-      <c r="D87" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E87" s="2"/>
-      <c r="F87" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="L87" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
-      <c r="P87" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q87" s="2"/>
-      <c r="R87" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S87" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T87" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AG87" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH87" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AI87" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ87" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AK87" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP87" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AQ87" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="AR87" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS87" t="s" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="88" hidden="true">
-      <c r="A88" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="D88" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="E88" s="2"/>
-      <c r="F88" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G88" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K88" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="L88" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="O88" s="2"/>
-      <c r="P88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q88" s="2"/>
-      <c r="R88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="AG88" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH88" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ88" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AQ88" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="AR88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS88" t="s" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="89" hidden="true">
-      <c r="A89" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="C89" s="2"/>
-      <c r="D89" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="E89" s="2"/>
-      <c r="F89" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G89" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H89" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I89" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="J89" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="K89" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="L89" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="P89" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q89" s="2"/>
-      <c r="R89" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S89" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T89" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U89" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V89" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W89" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X89" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Z89" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP89" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AQ89" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AR89" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS89" t="s" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="90" hidden="true">
-      <c r="A90" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="C90" s="2"/>
-      <c r="D90" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E90" s="2"/>
-      <c r="F90" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="G90" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="H90" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I90" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J90" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="K90" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="P90" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q90" s="2"/>
-      <c r="R90" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S90" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T90" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ90" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AK90" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="AP90" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AQ90" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="AR90" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AS90" t="s" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="91" hidden="true">
-      <c r="A91" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="C91" s="2"/>
-      <c r="D91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E91" s="2"/>
-      <c r="F91" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G91" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="H91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J91" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="K91" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="L91" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="P91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q91" s="2"/>
-      <c r="R91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="AG91" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ91" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AK91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="AP91" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="AQ91" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AR91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS91" t="s" s="2">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="92" hidden="true">
-      <c r="A92" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="C92" s="2"/>
-      <c r="D92" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E92" s="2"/>
-      <c r="F92" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G92" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="H92" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I92" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J92" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K92" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="L92" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="P92" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q92" s="2"/>
-      <c r="R92" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S92" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T92" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U92" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V92" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W92" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="AG92" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH92" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AI92" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="AJ92" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AK92" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL92" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP92" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AQ92" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="AR92" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS92" t="s" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="93" hidden="true">
-      <c r="A93" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="C93" s="2"/>
-      <c r="D93" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="E93" s="2"/>
-      <c r="F93" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H93" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I93" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J93" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K93" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="L93" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="P93" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q93" s="2"/>
-      <c r="R93" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S93" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T93" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U93" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V93" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W93" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X93" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="AG93" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI93" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ93" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AK93" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL93" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AP93" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AQ93" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="AR93" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS93" t="s" s="2">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="94" hidden="true">
-      <c r="A94" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="C94" s="2"/>
-      <c r="D94" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E94" s="2"/>
-      <c r="F94" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H94" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I94" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J94" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K94" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L94" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="P94" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q94" s="2"/>
-      <c r="R94" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S94" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T94" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="AG94" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI94" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ94" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AK94" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL94" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP94" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="AQ94" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="AR94" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS94" t="s" s="2">
         <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS94">
+  <autoFilter ref="A1:AS85">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14691,7 +13435,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI93">
+  <conditionalFormatting sqref="A2:AI84">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ObservationEXAM.xlsx
+++ b/docs/StructureDefinition-ObservationEXAM.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
